--- a/pricing/output/trinity-pricing-text.xlsx
+++ b/pricing/output/trinity-pricing-text.xlsx
@@ -564,10 +564,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -599,10 +599,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -850,7 +850,7 @@
     <col min="6" max="6" width="32.83203125" customWidth="1"/>
     <col min="7" max="7" width="34.83203125" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
-    <col min="9" max="9" width="31.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
     <col min="10" max="10" width="56.83203125" customWidth="1"/>
     <col min="11" max="11" width="44.83203125" customWidth="1"/>
     <col min="12" max="12" width="44.83203125" customWidth="1"/>
@@ -1375,16 +1375,16 @@
         <v>入 $0.14 · 出 $0.28 · 缓 $0.0028</v>
       </c>
       <c r="O7" s="7" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="P7" s="7" t="str">
-        <v>0%</v>
+        <v>+186%</v>
       </c>
       <c r="Q7" s="7" t="str">
-        <v>0%</v>
+        <v>+329%</v>
       </c>
       <c r="R7" s="7" t="str">
-        <v>0%</v>
+        <v>+355%</v>
       </c>
       <c r="S7" s="7" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1399,7 +1399,7 @@
         <v>入⚠-36.3% 出⚠-36.3% 缓⚠+550%</v>
       </c>
       <c r="W7" s="7" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠+186% 出⚠+329% 缓⚠+355%</v>
       </c>
       <c r="X7" s="7" t="str">
         <v>intl</v>
@@ -1452,16 +1452,16 @@
         <v>入 $0.435 · 出 $0.87 · 缓 $0.003625</v>
       </c>
       <c r="O8" s="7" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="P8" s="7" t="str">
-        <v>0%</v>
+        <v>+186%</v>
       </c>
       <c r="Q8" s="7" t="str">
-        <v>0%</v>
+        <v>+329%</v>
       </c>
       <c r="R8" s="7" t="str">
-        <v>0%</v>
+        <v>+1044%</v>
       </c>
       <c r="S8" s="7" t="str">
         <v>入✅ 出✅ 缓✅</v>
@@ -1476,7 +1476,7 @@
         <v>入⚠-5.8% 出⚠-5.8% 缓⚠-5.7%</v>
       </c>
       <c r="W8" s="7" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠+186% 出⚠+329% 缓⚠+1044%</v>
       </c>
       <c r="X8" s="7" t="str">
         <v>intl</v>
@@ -2802,10 +2802,10 @@
         <v>gpt-4.1</v>
       </c>
       <c r="C26" s="14" t="str">
-        <v>GPT-4.1</v>
+        <v>GPT</v>
       </c>
       <c r="D26" s="14" t="str">
-        <v>OpenAI</v>
+        <v>GPT</v>
       </c>
       <c r="E26" s="14" t="str">
         <v>标准价</v>
@@ -2814,16 +2814,16 @@
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="G26" s="14" t="str">
-        <v>入 ¥15 · 出 ¥60 · 缓 ¥3.75</v>
+        <v>—</v>
       </c>
       <c r="H26" s="14" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="I26" s="14" t="str">
         <v>—</v>
       </c>
       <c r="J26" s="14" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="K26" s="14" t="str">
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
@@ -2838,31 +2838,31 @@
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="O26" s="14" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="P26" s="14" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="Q26" s="14" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="R26" s="14" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="S26" s="14" t="str">
-        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
+        <v>—</v>
       </c>
       <c r="T26" s="14" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="U26" s="14" t="str">
         <v>—</v>
       </c>
       <c r="V26" s="14" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="W26" s="14" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>— 未上架</v>
       </c>
       <c r="X26" s="14" t="str">
         <v>usd-direct</v>
@@ -2879,10 +2879,10 @@
         <v>gpt-4o</v>
       </c>
       <c r="C27" s="13" t="str">
-        <v>GPT-4o</v>
+        <v>GPT</v>
       </c>
       <c r="D27" s="13" t="str">
-        <v>OpenAI</v>
+        <v>GPT</v>
       </c>
       <c r="E27" s="13" t="str">
         <v>标准价</v>
@@ -2891,16 +2891,16 @@
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="G27" s="13" t="str">
-        <v>入 ¥18.75 · 出 ¥75 · 缓 ¥9.37</v>
+        <v>—</v>
       </c>
       <c r="H27" s="13" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>—</v>
       </c>
       <c r="I27" s="13" t="str">
         <v>—</v>
       </c>
       <c r="J27" s="13" t="str">
-        <v>入 $2.5 · 出 $10</v>
+        <v>—</v>
       </c>
       <c r="K27" s="13" t="str">
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
@@ -2915,31 +2915,31 @@
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="O27" s="13" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>—</v>
       </c>
       <c r="P27" s="13" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="Q27" s="13" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="R27" s="13" t="str">
-        <v>0%</v>
+        <v>—</v>
       </c>
       <c r="S27" s="13" t="str">
-        <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.3%</v>
+        <v>—</v>
       </c>
       <c r="T27" s="13" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>—</v>
       </c>
       <c r="U27" s="13" t="str">
         <v>—</v>
       </c>
       <c r="V27" s="13" t="str">
-        <v>入✅ 出✅</v>
+        <v>—</v>
       </c>
       <c r="W27" s="13" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>— 未上架</v>
       </c>
       <c r="X27" s="13" t="str">
         <v>usd-direct</v>
@@ -2949,1927 +2949,1927 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="str">
+      <c r="A28" s="15" t="str">
         <v>gpt-5</v>
       </c>
-      <c r="B28" s="13" t="str">
+      <c r="B28" s="16" t="str">
         <v>gpt-5</v>
       </c>
-      <c r="C28" s="13" t="str">
+      <c r="C28" s="16" t="str">
         <v>GPT-5</v>
       </c>
-      <c r="D28" s="13" t="str">
+      <c r="D28" s="16" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E28" s="13" t="str">
+      <c r="E28" s="16" t="str">
         <v>标准价</v>
       </c>
-      <c r="F28" s="13" t="str">
+      <c r="F28" s="16" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="G28" s="13" t="str">
+      <c r="G28" s="16" t="str">
         <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
       </c>
-      <c r="H28" s="13" t="str">
+      <c r="H28" s="16" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="I28" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J28" s="13" t="str">
+      <c r="I28" s="16" t="str">
+        <v>—</v>
+      </c>
+      <c r="J28" s="16" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="K28" s="13" t="str">
+      <c r="K28" s="16" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="L28" s="13" t="str">
+      <c r="L28" s="16" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="M28" s="13" t="str">
+      <c r="M28" s="16" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N28" s="13" t="str">
+      <c r="N28" s="16" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="O28" s="13" t="str">
+      <c r="O28" s="16" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="P28" s="13" t="str">
+      <c r="P28" s="16" t="str">
         <v>0%</v>
       </c>
-      <c r="Q28" s="13" t="str">
+      <c r="Q28" s="16" t="str">
         <v>0%</v>
       </c>
-      <c r="R28" s="13" t="str">
+      <c r="R28" s="16" t="str">
         <v>0%</v>
       </c>
-      <c r="S28" s="13" t="str">
+      <c r="S28" s="16" t="str">
         <v>入⚠+15.3% 出⚠+15.4% 缓⚠+14.5%</v>
       </c>
-      <c r="T28" s="13" t="str">
+      <c r="T28" s="16" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U28" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V28" s="13" t="str">
+      <c r="U28" s="16" t="str">
+        <v>—</v>
+      </c>
+      <c r="V28" s="16" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="W28" s="13" t="str">
+      <c r="W28" s="16" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X28" s="13" t="str">
+      <c r="X28" s="16" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y28" s="13" t="str">
+      <c r="Y28" s="16" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="str">
+      <c r="A29" s="13" t="str">
         <v>gpt-5-mini</v>
       </c>
-      <c r="B29" s="16" t="str">
+      <c r="B29" s="13" t="str">
         <v>gpt-5-mini</v>
       </c>
-      <c r="C29" s="16" t="str">
+      <c r="C29" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="D29" s="16" t="str">
+      <c r="D29" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="E29" s="16" t="str">
+      <c r="E29" s="13" t="str">
         <v>标准价</v>
       </c>
-      <c r="F29" s="16" t="str">
+      <c r="F29" s="13" t="str">
         <v>入 $0.25 · 出 $2 · 缓 $0.025</v>
       </c>
-      <c r="G29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="H29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="I29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="J29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="K29" s="16" t="str">
+      <c r="G29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="H29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="I29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="J29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="K29" s="13" t="str">
         <v>入 $0.25 · 出 $2 · 缓 $0.025</v>
       </c>
-      <c r="L29" s="16" t="str">
+      <c r="L29" s="13" t="str">
         <v>入 $0.25 · 出 $2 · 缓 $0.025</v>
       </c>
-      <c r="M29" s="16" t="str">
+      <c r="M29" s="13" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N29" s="16" t="str">
+      <c r="N29" s="13" t="str">
         <v>入 $0.25 · 出 $2 · 缓 $0.025</v>
       </c>
-      <c r="O29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="P29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="Q29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="R29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="S29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="T29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="U29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="V29" s="16" t="str">
-        <v>—</v>
-      </c>
-      <c r="W29" s="16" t="str">
+      <c r="O29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="P29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="R29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="S29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="T29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="U29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="V29" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="W29" s="13" t="str">
         <v>— 未上架</v>
       </c>
-      <c r="X29" s="16" t="str">
+      <c r="X29" s="13" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y29" s="16" t="str">
+      <c r="Y29" s="13" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="str">
+      <c r="A30" s="15" t="str">
         <v>gpt-5-nano</v>
       </c>
-      <c r="B30" s="13" t="str">
+      <c r="B30" s="15" t="str">
         <v>gpt-5-nano</v>
       </c>
-      <c r="C30" s="13" t="str">
+      <c r="C30" s="15" t="str">
         <v>GPT-5 Nano</v>
       </c>
-      <c r="D30" s="13" t="str">
+      <c r="D30" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E30" s="13" t="str">
+      <c r="E30" s="15" t="str">
         <v>标准价</v>
       </c>
-      <c r="F30" s="13" t="str">
+      <c r="F30" s="15" t="str">
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
-      <c r="G30" s="13" t="str">
+      <c r="G30" s="15" t="str">
         <v>入 ¥0.37 · 出 ¥3 · 缓 ¥0.03</v>
       </c>
-      <c r="H30" s="13" t="str">
+      <c r="H30" s="15" t="str">
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
-      <c r="I30" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J30" s="13" t="str">
+      <c r="I30" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J30" s="15" t="str">
         <v>入 $0.049999999999999996 · 出 $0.39999999999999997 · 缓 $0.01</v>
       </c>
-      <c r="K30" s="13" t="str">
+      <c r="K30" s="15" t="str">
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
-      <c r="L30" s="13" t="str">
+      <c r="L30" s="15" t="str">
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
-      <c r="M30" s="13" t="str">
+      <c r="M30" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N30" s="13" t="str">
+      <c r="N30" s="15" t="str">
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
-      <c r="O30" s="13" t="str">
+      <c r="O30" s="15" t="str">
         <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
-      <c r="P30" s="13" t="str">
+      <c r="P30" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q30" s="13" t="str">
+      <c r="Q30" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R30" s="13" t="str">
+      <c r="R30" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S30" s="13" t="str">
+      <c r="S30" s="15" t="str">
         <v>入⚠+13.8% 出⚠+15.4% 缓⚠-7.7%</v>
       </c>
-      <c r="T30" s="13" t="str">
+      <c r="T30" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U30" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V30" s="13" t="str">
+      <c r="U30" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V30" s="15" t="str">
         <v>入✅ 出✅ 缓⚠+100%</v>
       </c>
-      <c r="W30" s="13" t="str">
+      <c r="W30" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X30" s="13" t="str">
+      <c r="X30" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y30" s="13" t="str">
+      <c r="Y30" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="str">
+      <c r="A31" s="15" t="str">
         <v>gpt-5.1</v>
       </c>
-      <c r="B31" s="13" t="str">
+      <c r="B31" s="15" t="str">
         <v>gpt-5.1</v>
       </c>
-      <c r="C31" s="13" t="str">
+      <c r="C31" s="15" t="str">
         <v>GPT-5.1</v>
       </c>
-      <c r="D31" s="13" t="str">
+      <c r="D31" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E31" s="13" t="str">
+      <c r="E31" s="15" t="str">
         <v>标准价</v>
       </c>
-      <c r="F31" s="13" t="str">
+      <c r="F31" s="15" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="G31" s="13" t="str">
+      <c r="G31" s="15" t="str">
         <v>入 ¥8.75 · 出 ¥70 · 缓 ¥0.87</v>
       </c>
-      <c r="H31" s="13" t="str">
+      <c r="H31" s="15" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="I31" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J31" s="13" t="str">
+      <c r="I31" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J31" s="15" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.13</v>
       </c>
-      <c r="K31" s="13" t="str">
+      <c r="K31" s="15" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="L31" s="13" t="str">
+      <c r="L31" s="15" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="M31" s="13" t="str">
+      <c r="M31" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N31" s="13" t="str">
+      <c r="N31" s="15" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="O31" s="13" t="str">
+      <c r="O31" s="15" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="P31" s="13" t="str">
+      <c r="P31" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q31" s="13" t="str">
+      <c r="Q31" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R31" s="13" t="str">
+      <c r="R31" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S31" s="13" t="str">
+      <c r="S31" s="15" t="str">
         <v>入⚠+7.7% 出⚠+7.7% 缓⚠+7.1%</v>
       </c>
-      <c r="T31" s="13" t="str">
+      <c r="T31" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U31" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V31" s="13" t="str">
+      <c r="U31" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V31" s="15" t="str">
         <v>入✅ 出✅ 缓⚠+4%</v>
       </c>
-      <c r="W31" s="13" t="str">
+      <c r="W31" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X31" s="13" t="str">
+      <c r="X31" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y31" s="13" t="str">
+      <c r="Y31" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="str">
+      <c r="A32" s="15" t="str">
         <v>gpt-5.2</v>
       </c>
-      <c r="B32" s="13" t="str">
+      <c r="B32" s="15" t="str">
         <v>gpt-5.2</v>
       </c>
-      <c r="C32" s="13" t="str">
+      <c r="C32" s="15" t="str">
         <v>GPT-5.2</v>
       </c>
-      <c r="D32" s="13" t="str">
+      <c r="D32" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E32" s="13" t="str">
+      <c r="E32" s="15" t="str">
         <v>标准价</v>
       </c>
-      <c r="F32" s="13" t="str">
+      <c r="F32" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="G32" s="13" t="str">
+      <c r="G32" s="15" t="str">
         <v>入 ¥12.25 · 出 ¥98 · 缓 ¥1.22</v>
       </c>
-      <c r="H32" s="13" t="str">
+      <c r="H32" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="I32" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J32" s="13" t="str">
+      <c r="I32" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J32" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="K32" s="13" t="str">
+      <c r="K32" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="L32" s="13" t="str">
+      <c r="L32" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="M32" s="13" t="str">
+      <c r="M32" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N32" s="13" t="str">
+      <c r="N32" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="O32" s="13" t="str">
+      <c r="O32" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="P32" s="13" t="str">
+      <c r="P32" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q32" s="13" t="str">
+      <c r="Q32" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R32" s="13" t="str">
+      <c r="R32" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S32" s="13" t="str">
+      <c r="S32" s="15" t="str">
         <v>入⚠+7.7% 出⚠+7.7% 缓⚠+7.3%</v>
       </c>
-      <c r="T32" s="13" t="str">
+      <c r="T32" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U32" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V32" s="13" t="str">
+      <c r="U32" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V32" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="W32" s="13" t="str">
+      <c r="W32" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X32" s="13" t="str">
+      <c r="X32" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y32" s="13" t="str">
+      <c r="Y32" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="str">
+      <c r="A33" s="15" t="str">
         <v>gpt-5.3-codex</v>
       </c>
-      <c r="B33" s="13" t="str">
+      <c r="B33" s="15" t="str">
         <v>gpt-5.3-codex</v>
       </c>
-      <c r="C33" s="13" t="str">
+      <c r="C33" s="15" t="str">
         <v>GPT-5.3 Codex</v>
       </c>
-      <c r="D33" s="13" t="str">
+      <c r="D33" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E33" s="13" t="str">
+      <c r="E33" s="15" t="str">
         <v>标准价</v>
       </c>
-      <c r="F33" s="13" t="str">
+      <c r="F33" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="G33" s="13" t="str">
+      <c r="G33" s="15" t="str">
         <v>入 ¥13.13 · 出 ¥105 · 缓 ¥1.35</v>
       </c>
-      <c r="H33" s="13" t="str">
+      <c r="H33" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
       </c>
-      <c r="I33" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J33" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K33" s="13" t="str">
+      <c r="I33" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J33" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K33" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="L33" s="13" t="str">
+      <c r="L33" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="M33" s="13" t="str">
+      <c r="M33" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N33" s="13" t="str">
+      <c r="N33" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="O33" s="13" t="str">
+      <c r="O33" s="15" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="P33" s="13" t="str">
+      <c r="P33" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q33" s="13" t="str">
+      <c r="Q33" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R33" s="13" t="str">
+      <c r="R33" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S33" s="13" t="str">
+      <c r="S33" s="15" t="str">
         <v>入⚠+15.4% 出⚠+15.4% 缓⚠+18.7%</v>
       </c>
-      <c r="T33" s="13" t="str">
+      <c r="T33" s="15" t="str">
         <v>入✅ 出✅ 缓⚠+2.9%</v>
       </c>
-      <c r="U33" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V33" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="W33" s="13" t="str">
+      <c r="U33" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V33" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="W33" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X33" s="13" t="str">
+      <c r="X33" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y33" s="13" t="str">
+      <c r="Y33" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="str">
+      <c r="A34" s="15" t="str">
         <v>gpt-5.4</v>
       </c>
-      <c r="B34" s="13" t="str">
+      <c r="B34" s="15" t="str">
         <v>gpt-5.4</v>
       </c>
-      <c r="C34" s="13" t="str">
+      <c r="C34" s="15" t="str">
         <v>GPT-5.4</v>
       </c>
-      <c r="D34" s="13" t="str">
+      <c r="D34" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E34" s="13" t="str">
+      <c r="E34" s="15" t="str">
         <v>输入&lt;=272K context</v>
       </c>
-      <c r="F34" s="13" t="str">
+      <c r="F34" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="G34" s="13" t="str">
+      <c r="G34" s="15" t="str">
         <v>入 ¥18.75 · 出 ¥112.5 · 缓 ¥1.88</v>
       </c>
-      <c r="H34" s="13" t="str">
+      <c r="H34" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="I34" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J34" s="13" t="str">
+      <c r="I34" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J34" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="K34" s="13" t="str">
+      <c r="K34" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="L34" s="13" t="str">
+      <c r="L34" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="M34" s="13" t="str">
+      <c r="M34" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N34" s="13" t="str">
+      <c r="N34" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="O34" s="13" t="str">
+      <c r="O34" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="P34" s="13" t="str">
+      <c r="P34" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q34" s="13" t="str">
+      <c r="Q34" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R34" s="13" t="str">
+      <c r="R34" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S34" s="13" t="str">
+      <c r="S34" s="15" t="str">
         <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.7%</v>
       </c>
-      <c r="T34" s="13" t="str">
+      <c r="T34" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U34" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V34" s="13" t="str">
+      <c r="U34" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V34" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="W34" s="13" t="str">
+      <c r="W34" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X34" s="13" t="str">
+      <c r="X34" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y34" s="13" t="str">
+      <c r="Y34" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B35" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C35" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D35" s="13" t="str">
-        <v/>
-      </c>
-      <c r="E35" s="13" t="str">
+      <c r="A35" s="15" t="str">
+        <v/>
+      </c>
+      <c r="B35" s="15" t="str">
+        <v/>
+      </c>
+      <c r="C35" s="15" t="str">
+        <v/>
+      </c>
+      <c r="D35" s="15" t="str">
+        <v/>
+      </c>
+      <c r="E35" s="15" t="str">
         <v>输入&gt;272K context</v>
       </c>
-      <c r="F35" s="13" t="str">
+      <c r="F35" s="15" t="str">
         <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
-      <c r="G35" s="13" t="str">
+      <c r="G35" s="15" t="str">
         <v>入 ¥37.5 · 出 ¥168.75 · 缓 ¥3.75</v>
       </c>
-      <c r="H35" s="13" t="str">
+      <c r="H35" s="15" t="str">
         <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
-      <c r="I35" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J35" s="13" t="str">
+      <c r="I35" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J35" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="K35" s="13" t="str">
+      <c r="K35" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="L35" s="13" t="str">
+      <c r="L35" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="M35" s="13" t="str">
+      <c r="M35" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N35" s="13" t="str">
+      <c r="N35" s="15" t="str">
         <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
-      <c r="O35" s="13" t="str">
+      <c r="O35" s="15" t="str">
         <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
-      <c r="P35" s="13" t="str">
+      <c r="P35" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q35" s="13" t="str">
+      <c r="Q35" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R35" s="13" t="str">
+      <c r="R35" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S35" s="13" t="str">
+      <c r="S35" s="15" t="str">
         <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
-      <c r="T35" s="13" t="str">
+      <c r="T35" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U35" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V35" s="13" t="str">
+      <c r="U35" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V35" s="15" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="W35" s="13" t="str">
+      <c r="W35" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X35" s="13" t="str">
+      <c r="X35" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y35" s="13" t="str">
+      <c r="Y35" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="str">
+      <c r="A36" s="15" t="str">
         <v>gpt-5.4-mini</v>
       </c>
-      <c r="B36" s="13" t="str">
+      <c r="B36" s="15" t="str">
         <v>gpt-5.4-mini</v>
       </c>
-      <c r="C36" s="13" t="str">
+      <c r="C36" s="15" t="str">
         <v>GPT-5.4 Mini</v>
       </c>
-      <c r="D36" s="13" t="str">
+      <c r="D36" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E36" s="13" t="str">
+      <c r="E36" s="15" t="str">
         <v>标准价</v>
       </c>
-      <c r="F36" s="13" t="str">
+      <c r="F36" s="15" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
-      <c r="G36" s="13" t="str">
+      <c r="G36" s="15" t="str">
         <v>入 ¥5.63 · 出 ¥33.75 · 缓 ¥0.56</v>
       </c>
-      <c r="H36" s="13" t="str">
+      <c r="H36" s="15" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
-      <c r="I36" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J36" s="13" t="str">
+      <c r="I36" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J36" s="15" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
-      <c r="K36" s="13" t="str">
+      <c r="K36" s="15" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
-      <c r="L36" s="13" t="str">
+      <c r="L36" s="15" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
-      <c r="M36" s="13" t="str">
+      <c r="M36" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N36" s="13" t="str">
+      <c r="N36" s="15" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
-      <c r="O36" s="13" t="str">
+      <c r="O36" s="15" t="str">
         <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
-      <c r="P36" s="13" t="str">
+      <c r="P36" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q36" s="13" t="str">
+      <c r="Q36" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R36" s="13" t="str">
+      <c r="R36" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S36" s="13" t="str">
+      <c r="S36" s="15" t="str">
         <v>入⚠+15.5% 出⚠+15.4% 缓⚠+14.9%</v>
       </c>
-      <c r="T36" s="13" t="str">
+      <c r="T36" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U36" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V36" s="13" t="str">
+      <c r="U36" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V36" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="W36" s="13" t="str">
+      <c r="W36" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X36" s="13" t="str">
+      <c r="X36" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y36" s="13" t="str">
+      <c r="Y36" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="str">
+      <c r="A37" s="15" t="str">
         <v>gpt-5.4-nano</v>
       </c>
-      <c r="B37" s="13" t="str">
+      <c r="B37" s="15" t="str">
         <v>gpt-5.4-nano</v>
       </c>
-      <c r="C37" s="13" t="str">
+      <c r="C37" s="15" t="str">
         <v>GPT-5.4 nano</v>
       </c>
-      <c r="D37" s="13" t="str">
+      <c r="D37" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E37" s="13" t="str">
+      <c r="E37" s="15" t="str">
         <v>标准价</v>
       </c>
-      <c r="F37" s="13" t="str">
+      <c r="F37" s="15" t="str">
         <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
-      <c r="G37" s="13" t="str">
+      <c r="G37" s="15" t="str">
         <v>入 ¥1.5 · 出 ¥9.375 · 缓 ¥0.15</v>
       </c>
-      <c r="H37" s="13" t="str">
+      <c r="H37" s="15" t="str">
         <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
-      <c r="I37" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J37" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K37" s="13" t="str">
+      <c r="I37" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J37" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K37" s="15" t="str">
         <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
-      <c r="L37" s="13" t="str">
+      <c r="L37" s="15" t="str">
         <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
-      <c r="M37" s="13" t="str">
+      <c r="M37" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N37" s="13" t="str">
+      <c r="N37" s="15" t="str">
         <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
-      <c r="O37" s="13" t="str">
+      <c r="O37" s="15" t="str">
         <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
-      <c r="P37" s="13" t="str">
+      <c r="P37" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q37" s="13" t="str">
+      <c r="Q37" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R37" s="13" t="str">
+      <c r="R37" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S37" s="13" t="str">
+      <c r="S37" s="15" t="str">
         <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
-      <c r="T37" s="13" t="str">
+      <c r="T37" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U37" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V37" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="W37" s="13" t="str">
+      <c r="U37" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V37" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="W37" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X37" s="13" t="str">
+      <c r="X37" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y37" s="13" t="str">
+      <c r="Y37" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="str">
+      <c r="A38" s="15" t="str">
         <v>gpt-5.4-pro</v>
       </c>
-      <c r="B38" s="13" t="str">
+      <c r="B38" s="15" t="str">
         <v>gpt-5.4-pro</v>
       </c>
-      <c r="C38" s="13" t="str">
+      <c r="C38" s="15" t="str">
         <v>GPT-5.4 Pro</v>
       </c>
-      <c r="D38" s="13" t="str">
+      <c r="D38" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E38" s="13" t="str">
+      <c r="E38" s="15" t="str">
         <v>输入&lt;=272K context</v>
       </c>
-      <c r="F38" s="13" t="str">
+      <c r="F38" s="15" t="str">
         <v>入 $30 · 出 $180</v>
       </c>
-      <c r="G38" s="13" t="str">
+      <c r="G38" s="15" t="str">
         <v>入 ¥225 · 出 ¥1350</v>
       </c>
-      <c r="H38" s="13" t="str">
+      <c r="H38" s="15" t="str">
         <v>入 $30 · 出 $180</v>
       </c>
-      <c r="I38" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J38" s="13" t="str">
+      <c r="I38" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J38" s="15" t="str">
         <v>入 $30 · 出 $180</v>
       </c>
-      <c r="K38" s="13" t="str">
+      <c r="K38" s="15" t="str">
         <v>入 $30 · 出 $180 · 缓 $⚠</v>
       </c>
-      <c r="L38" s="13" t="str">
+      <c r="L38" s="15" t="str">
         <v>入 $30 · 出 $180 · 缓 $⚠</v>
       </c>
-      <c r="M38" s="13" t="str">
+      <c r="M38" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N38" s="13" t="str">
+      <c r="N38" s="15" t="str">
         <v>入 $30 · 出 $180 · 缓 $⚠</v>
       </c>
-      <c r="O38" s="13" t="str">
+      <c r="O38" s="15" t="str">
         <v>入 $30 · 出 $180</v>
       </c>
-      <c r="P38" s="13" t="str">
+      <c r="P38" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q38" s="13" t="str">
+      <c r="Q38" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R38" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="S38" s="13" t="str">
+      <c r="R38" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="S38" s="15" t="str">
         <v>入⚠+15.4% 出⚠+15.4%</v>
       </c>
-      <c r="T38" s="13" t="str">
+      <c r="T38" s="15" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="U38" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V38" s="13" t="str">
+      <c r="U38" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V38" s="15" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="W38" s="13" t="str">
+      <c r="W38" s="15" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="X38" s="13" t="str">
+      <c r="X38" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y38" s="13" t="str">
+      <c r="Y38" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B39" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C39" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D39" s="13" t="str">
-        <v/>
-      </c>
-      <c r="E39" s="13" t="str">
+      <c r="A39" s="15" t="str">
+        <v/>
+      </c>
+      <c r="B39" s="15" t="str">
+        <v/>
+      </c>
+      <c r="C39" s="15" t="str">
+        <v/>
+      </c>
+      <c r="D39" s="15" t="str">
+        <v/>
+      </c>
+      <c r="E39" s="15" t="str">
         <v>输入&gt;272K context</v>
       </c>
-      <c r="F39" s="13" t="str">
+      <c r="F39" s="15" t="str">
         <v>入 $60 · 出 $270</v>
       </c>
-      <c r="G39" s="13" t="str">
+      <c r="G39" s="15" t="str">
         <v>入 ¥450 · 出 ¥2025</v>
       </c>
-      <c r="H39" s="13" t="str">
+      <c r="H39" s="15" t="str">
         <v>入 $60 · 出 $270</v>
       </c>
-      <c r="I39" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J39" s="13" t="str">
+      <c r="I39" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J39" s="15" t="str">
         <v>入 $30 · 出 $180</v>
       </c>
-      <c r="K39" s="13" t="str">
+      <c r="K39" s="15" t="str">
         <v>入 $30 · 出 $180 · 缓 $⚠</v>
       </c>
-      <c r="L39" s="13" t="str">
+      <c r="L39" s="15" t="str">
         <v>入 $30 · 出 $180 · 缓 $⚠</v>
       </c>
-      <c r="M39" s="13" t="str">
+      <c r="M39" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N39" s="13" t="str">
+      <c r="N39" s="15" t="str">
         <v>入 $30 · 出 $180 · 缓 $⚠</v>
       </c>
-      <c r="O39" s="13" t="str">
+      <c r="O39" s="15" t="str">
         <v>入 $60 · 出 $270</v>
       </c>
-      <c r="P39" s="13" t="str">
+      <c r="P39" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q39" s="13" t="str">
+      <c r="Q39" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R39" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="S39" s="13" t="str">
+      <c r="R39" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="S39" s="15" t="str">
         <v>入⚠+15.4% 出⚠+15.4%</v>
       </c>
-      <c r="T39" s="13" t="str">
+      <c r="T39" s="15" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="U39" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V39" s="13" t="str">
+      <c r="U39" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V39" s="15" t="str">
         <v>入⚠-50% 出⚠-33.3%</v>
       </c>
-      <c r="W39" s="13" t="str">
+      <c r="W39" s="15" t="str">
         <v>入✅ 出✅</v>
       </c>
-      <c r="X39" s="13" t="str">
+      <c r="X39" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y39" s="13" t="str">
+      <c r="Y39" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="str">
+      <c r="A40" s="15" t="str">
         <v>gpt-5.5</v>
       </c>
-      <c r="B40" s="13" t="str">
+      <c r="B40" s="15" t="str">
         <v>gpt-5.5</v>
       </c>
-      <c r="C40" s="13" t="str">
+      <c r="C40" s="15" t="str">
         <v>GPT-5.5</v>
       </c>
-      <c r="D40" s="13" t="str">
+      <c r="D40" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E40" s="13" t="str">
+      <c r="E40" s="15" t="str">
         <v>输入&lt;=272K context</v>
       </c>
-      <c r="F40" s="13" t="str">
+      <c r="F40" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="G40" s="13" t="str">
+      <c r="G40" s="15" t="str">
         <v>入 ¥37.5 · 出 ¥225 · 缓 ¥3.75</v>
       </c>
-      <c r="H40" s="13" t="str">
+      <c r="H40" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="I40" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J40" s="13" t="str">
+      <c r="I40" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J40" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="K40" s="13" t="str">
+      <c r="K40" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="L40" s="13" t="str">
+      <c r="L40" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="M40" s="13" t="str">
+      <c r="M40" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N40" s="13" t="str">
+      <c r="N40" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="O40" s="13" t="str">
+      <c r="O40" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="P40" s="13" t="str">
+      <c r="P40" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q40" s="13" t="str">
+      <c r="Q40" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R40" s="13" t="str">
+      <c r="R40" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S40" s="13" t="str">
+      <c r="S40" s="15" t="str">
         <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
-      <c r="T40" s="13" t="str">
+      <c r="T40" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U40" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V40" s="13" t="str">
+      <c r="U40" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V40" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="W40" s="13" t="str">
+      <c r="W40" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X40" s="13" t="str">
+      <c r="X40" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y40" s="13" t="str">
+      <c r="Y40" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B41" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C41" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D41" s="13" t="str">
-        <v/>
-      </c>
-      <c r="E41" s="13" t="str">
+      <c r="A41" s="15" t="str">
+        <v/>
+      </c>
+      <c r="B41" s="15" t="str">
+        <v/>
+      </c>
+      <c r="C41" s="15" t="str">
+        <v/>
+      </c>
+      <c r="D41" s="15" t="str">
+        <v/>
+      </c>
+      <c r="E41" s="15" t="str">
         <v>输入&gt;272K context</v>
       </c>
-      <c r="F41" s="13" t="str">
+      <c r="F41" s="15" t="str">
         <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
-      <c r="G41" s="13" t="str">
+      <c r="G41" s="15" t="str">
         <v>入 ¥75 · 出 ¥337.5 · 缓 ¥7.5</v>
       </c>
-      <c r="H41" s="13" t="str">
+      <c r="H41" s="15" t="str">
         <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
-      <c r="I41" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J41" s="13" t="str">
+      <c r="I41" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J41" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="K41" s="13" t="str">
+      <c r="K41" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="L41" s="13" t="str">
+      <c r="L41" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="M41" s="13" t="str">
+      <c r="M41" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N41" s="13" t="str">
+      <c r="N41" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="O41" s="13" t="str">
+      <c r="O41" s="15" t="str">
         <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
-      <c r="P41" s="13" t="str">
+      <c r="P41" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q41" s="13" t="str">
+      <c r="Q41" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R41" s="13" t="str">
+      <c r="R41" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S41" s="13" t="str">
+      <c r="S41" s="15" t="str">
         <v>入⚠+15.4% 出⚠+15.4% 缓⚠+15.4%</v>
       </c>
-      <c r="T41" s="13" t="str">
+      <c r="T41" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="U41" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V41" s="13" t="str">
+      <c r="U41" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V41" s="15" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="W41" s="13" t="str">
+      <c r="W41" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X41" s="13" t="str">
+      <c r="X41" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y41" s="13" t="str">
+      <c r="Y41" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="str">
+      <c r="A42" s="15" t="str">
         <v>gpt-5.6-luna</v>
       </c>
-      <c r="B42" s="13" t="str">
+      <c r="B42" s="15" t="str">
         <v>gpt-5.6-luna</v>
       </c>
-      <c r="C42" s="13" t="str">
+      <c r="C42" s="15" t="str">
         <v>GPT-5.6 Luna</v>
       </c>
-      <c r="D42" s="13" t="str">
+      <c r="D42" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E42" s="13" t="str">
+      <c r="E42" s="15" t="str">
         <v>输入&lt;=272K context</v>
       </c>
-      <c r="F42" s="13" t="str">
+      <c r="F42" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="G42" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="H42" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="I42" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J42" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K42" s="13" t="str">
+      <c r="G42" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="H42" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="I42" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J42" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K42" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="L42" s="13" t="str">
+      <c r="L42" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="M42" s="13" t="str">
+      <c r="M42" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N42" s="13" t="str">
+      <c r="N42" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="O42" s="13" t="str">
+      <c r="O42" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="P42" s="13" t="str">
+      <c r="P42" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q42" s="13" t="str">
+      <c r="Q42" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R42" s="13" t="str">
+      <c r="R42" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S42" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="T42" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="U42" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V42" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="W42" s="13" t="str">
+      <c r="S42" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="T42" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="U42" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V42" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="W42" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X42" s="13" t="str">
+      <c r="X42" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y42" s="13" t="str">
+      <c r="Y42" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B43" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C43" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D43" s="13" t="str">
-        <v/>
-      </c>
-      <c r="E43" s="13" t="str">
+      <c r="A43" s="15" t="str">
+        <v/>
+      </c>
+      <c r="B43" s="15" t="str">
+        <v/>
+      </c>
+      <c r="C43" s="15" t="str">
+        <v/>
+      </c>
+      <c r="D43" s="15" t="str">
+        <v/>
+      </c>
+      <c r="E43" s="15" t="str">
         <v>输入&gt;272K context</v>
       </c>
-      <c r="F43" s="13" t="str">
+      <c r="F43" s="15" t="str">
         <v>入 $0.4 · 出 $1.8 · 缓 $0.04</v>
       </c>
-      <c r="G43" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="H43" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="I43" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J43" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K43" s="13" t="str">
+      <c r="G43" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="H43" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="I43" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J43" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K43" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="L43" s="13" t="str">
+      <c r="L43" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="M43" s="13" t="str">
+      <c r="M43" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N43" s="13" t="str">
+      <c r="N43" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="O43" s="13" t="str">
+      <c r="O43" s="15" t="str">
         <v>入 $0.2 · 出 $1.2 · 缓 $0.02</v>
       </c>
-      <c r="P43" s="13" t="str">
+      <c r="P43" s="15" t="str">
         <v>-50%</v>
       </c>
-      <c r="Q43" s="13" t="str">
+      <c r="Q43" s="15" t="str">
         <v>-33.3%</v>
       </c>
-      <c r="R43" s="13" t="str">
+      <c r="R43" s="15" t="str">
         <v>-50%</v>
       </c>
-      <c r="S43" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="T43" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="U43" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V43" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="W43" s="13" t="str">
+      <c r="S43" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="T43" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="U43" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V43" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="W43" s="15" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="X43" s="13" t="str">
+      <c r="X43" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y43" s="13" t="str">
+      <c r="Y43" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="str">
+      <c r="A44" s="15" t="str">
         <v>gpt-5.6-sol</v>
       </c>
-      <c r="B44" s="13" t="str">
+      <c r="B44" s="15" t="str">
         <v>gpt-5.6-sol</v>
       </c>
-      <c r="C44" s="13" t="str">
+      <c r="C44" s="15" t="str">
         <v>GPT-5.6 Sol</v>
       </c>
-      <c r="D44" s="13" t="str">
+      <c r="D44" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E44" s="13" t="str">
+      <c r="E44" s="15" t="str">
         <v>输入&lt;=272K context</v>
       </c>
-      <c r="F44" s="13" t="str">
+      <c r="F44" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="G44" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="H44" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="I44" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J44" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K44" s="13" t="str">
+      <c r="G44" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="H44" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="I44" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J44" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K44" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="L44" s="13" t="str">
+      <c r="L44" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="M44" s="13" t="str">
+      <c r="M44" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N44" s="13" t="str">
+      <c r="N44" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="O44" s="13" t="str">
+      <c r="O44" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="P44" s="13" t="str">
+      <c r="P44" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q44" s="13" t="str">
+      <c r="Q44" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R44" s="13" t="str">
+      <c r="R44" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S44" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="T44" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="U44" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V44" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="W44" s="13" t="str">
+      <c r="S44" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="T44" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="U44" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V44" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="W44" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X44" s="13" t="str">
+      <c r="X44" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y44" s="13" t="str">
+      <c r="Y44" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B45" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C45" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D45" s="13" t="str">
-        <v/>
-      </c>
-      <c r="E45" s="13" t="str">
+      <c r="A45" s="15" t="str">
+        <v/>
+      </c>
+      <c r="B45" s="15" t="str">
+        <v/>
+      </c>
+      <c r="C45" s="15" t="str">
+        <v/>
+      </c>
+      <c r="D45" s="15" t="str">
+        <v/>
+      </c>
+      <c r="E45" s="15" t="str">
         <v>输入&gt;272K context</v>
       </c>
-      <c r="F45" s="13" t="str">
+      <c r="F45" s="15" t="str">
         <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
-      <c r="G45" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="H45" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="I45" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J45" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K45" s="13" t="str">
+      <c r="G45" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="H45" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="I45" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J45" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K45" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="L45" s="13" t="str">
+      <c r="L45" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="M45" s="13" t="str">
+      <c r="M45" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N45" s="13" t="str">
+      <c r="N45" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="O45" s="13" t="str">
+      <c r="O45" s="15" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="P45" s="13" t="str">
+      <c r="P45" s="15" t="str">
         <v>-50%</v>
       </c>
-      <c r="Q45" s="13" t="str">
+      <c r="Q45" s="15" t="str">
         <v>-33.3%</v>
       </c>
-      <c r="R45" s="13" t="str">
+      <c r="R45" s="15" t="str">
         <v>-50%</v>
       </c>
-      <c r="S45" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="T45" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="U45" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V45" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="W45" s="13" t="str">
+      <c r="S45" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="T45" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="U45" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V45" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="W45" s="15" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="X45" s="13" t="str">
+      <c r="X45" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y45" s="13" t="str">
+      <c r="Y45" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="str">
+      <c r="A46" s="15" t="str">
         <v>gpt-5.6-terra</v>
       </c>
-      <c r="B46" s="13" t="str">
+      <c r="B46" s="15" t="str">
         <v>gpt-5.6-terra</v>
       </c>
-      <c r="C46" s="13" t="str">
+      <c r="C46" s="15" t="str">
         <v>GPT-5.6 Terra</v>
       </c>
-      <c r="D46" s="13" t="str">
+      <c r="D46" s="15" t="str">
         <v>OpenAI</v>
       </c>
-      <c r="E46" s="13" t="str">
+      <c r="E46" s="15" t="str">
         <v>输入&lt;=272K context</v>
       </c>
-      <c r="F46" s="13" t="str">
+      <c r="F46" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="G46" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="H46" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="I46" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J46" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K46" s="13" t="str">
+      <c r="G46" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="H46" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="I46" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J46" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K46" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="L46" s="13" t="str">
+      <c r="L46" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="M46" s="13" t="str">
+      <c r="M46" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N46" s="13" t="str">
+      <c r="N46" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="O46" s="13" t="str">
+      <c r="O46" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="P46" s="13" t="str">
+      <c r="P46" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="Q46" s="13" t="str">
+      <c r="Q46" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="R46" s="13" t="str">
+      <c r="R46" s="15" t="str">
         <v>0%</v>
       </c>
-      <c r="S46" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="T46" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="U46" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V46" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="W46" s="13" t="str">
+      <c r="S46" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="T46" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="U46" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V46" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="W46" s="15" t="str">
         <v>入✅ 出✅ 缓✅</v>
       </c>
-      <c r="X46" s="13" t="str">
+      <c r="X46" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y46" s="13" t="str">
+      <c r="Y46" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B47" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C47" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D47" s="13" t="str">
-        <v/>
-      </c>
-      <c r="E47" s="13" t="str">
+      <c r="A47" s="15" t="str">
+        <v/>
+      </c>
+      <c r="B47" s="15" t="str">
+        <v/>
+      </c>
+      <c r="C47" s="15" t="str">
+        <v/>
+      </c>
+      <c r="D47" s="15" t="str">
+        <v/>
+      </c>
+      <c r="E47" s="15" t="str">
         <v>输入&gt;272K context</v>
       </c>
-      <c r="F47" s="13" t="str">
+      <c r="F47" s="15" t="str">
         <v>入 $4 · 出 $18 · 缓 $0.4</v>
       </c>
-      <c r="G47" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="H47" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="I47" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="J47" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="K47" s="13" t="str">
+      <c r="G47" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="H47" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="I47" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="J47" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="K47" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="L47" s="13" t="str">
+      <c r="L47" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="M47" s="13" t="str">
+      <c r="M47" s="15" t="str">
         <v>入 = / 出 =</v>
       </c>
-      <c r="N47" s="13" t="str">
+      <c r="N47" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="O47" s="13" t="str">
+      <c r="O47" s="15" t="str">
         <v>入 $2 · 出 $12 · 缓 $0.2</v>
       </c>
-      <c r="P47" s="13" t="str">
+      <c r="P47" s="15" t="str">
         <v>-50%</v>
       </c>
-      <c r="Q47" s="13" t="str">
+      <c r="Q47" s="15" t="str">
         <v>-33.3%</v>
       </c>
-      <c r="R47" s="13" t="str">
+      <c r="R47" s="15" t="str">
         <v>-50%</v>
       </c>
-      <c r="S47" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="T47" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="U47" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="V47" s="13" t="str">
-        <v>—</v>
-      </c>
-      <c r="W47" s="13" t="str">
+      <c r="S47" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="T47" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="U47" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="V47" s="15" t="str">
+        <v>—</v>
+      </c>
+      <c r="W47" s="15" t="str">
         <v>入⚠-50% 出⚠-33.3% 缓⚠-50%</v>
       </c>
-      <c r="X47" s="13" t="str">
+      <c r="X47" s="15" t="str">
         <v>usd-direct</v>
       </c>
-      <c r="Y47" s="13" t="str">
+      <c r="Y47" s="15" t="str">
         <v>国际-only / 已是 USD · V2=V1</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="str">
+      <c r="A48" s="13" t="str">
         <v>chat-latest</v>
       </c>
-      <c r="B48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="C48" s="15" t="str">
+      <c r="B48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="C48" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="D48" s="15" t="str">
+      <c r="D48" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="E48" s="15" t="str">
+      <c r="E48" s="13" t="str">
         <v>输入&lt;=272K context</v>
       </c>
-      <c r="F48" s="15" t="str">
+      <c r="F48" s="13" t="str">
         <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
-      <c r="G48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="H48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="I48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="J48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="K48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="L48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="M48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="N48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="O48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="P48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Q48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="R48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="S48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="T48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="U48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="V48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="W48" s="15" t="str">
+      <c r="G48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="H48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="I48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="J48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="K48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="L48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="M48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="N48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="O48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="P48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="R48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="S48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="T48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="U48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="V48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="W48" s="13" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="X48" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Y48" s="15" t="str">
+      <c r="X48" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Y48" s="13" t="str">
         <v>对应 gpt-5.5 instant</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="str">
-        <v/>
-      </c>
-      <c r="B49" s="15" t="str">
-        <v/>
-      </c>
-      <c r="C49" s="15" t="str">
-        <v/>
-      </c>
-      <c r="D49" s="15" t="str">
-        <v/>
-      </c>
-      <c r="E49" s="15" t="str">
+      <c r="A49" s="13" t="str">
+        <v/>
+      </c>
+      <c r="B49" s="13" t="str">
+        <v/>
+      </c>
+      <c r="C49" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D49" s="13" t="str">
+        <v/>
+      </c>
+      <c r="E49" s="13" t="str">
         <v>输入&gt;272K context</v>
       </c>
-      <c r="F49" s="15" t="str">
+      <c r="F49" s="13" t="str">
         <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
-      <c r="G49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="H49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="I49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="J49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="K49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="L49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="M49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="N49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="O49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="P49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Q49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="R49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="S49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="T49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="U49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="V49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="W49" s="15" t="str">
+      <c r="G49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="H49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="I49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="J49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="K49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="L49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="M49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="N49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="O49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="P49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="R49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="S49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="T49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="U49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="V49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="W49" s="13" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="X49" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Y49" s="15" t="str">
+      <c r="X49" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Y49" s="13" t="str">
         <v>对应 gpt-5.5 instant</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="str">
+      <c r="A50" s="13" t="str">
         <v>gpt-5.1-chat</v>
       </c>
-      <c r="B50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="C50" s="15" t="str">
+      <c r="B50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="C50" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="D50" s="15" t="str">
+      <c r="D50" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="E50" s="15" t="str">
+      <c r="E50" s="13" t="str">
         <v>标准价</v>
       </c>
-      <c r="F50" s="15" t="str">
+      <c r="F50" s="13" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="G50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="H50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="I50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="J50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="K50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="L50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="M50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="N50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="O50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="P50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Q50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="R50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="S50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="T50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="U50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="V50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="W50" s="15" t="str">
+      <c r="G50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="H50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="I50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="J50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="K50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="L50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="M50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="N50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="O50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="P50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="R50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="S50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="T50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="U50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="V50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="W50" s="13" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="X50" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Y50" s="15" t="str">
+      <c r="X50" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Y50" s="13" t="str">
         <v>线上 slug gpt-5.1-chat；价同 chat-latest</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="str">
+      <c r="A51" s="13" t="str">
         <v>gpt-5.2-chat-latest</v>
       </c>
-      <c r="B51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="C51" s="15" t="str">
+      <c r="B51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="C51" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="D51" s="15" t="str">
+      <c r="D51" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="E51" s="15" t="str">
+      <c r="E51" s="13" t="str">
         <v>标准价</v>
       </c>
-      <c r="F51" s="15" t="str">
+      <c r="F51" s="13" t="str">
         <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
-      <c r="G51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="H51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="I51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="J51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="K51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="L51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="M51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="N51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="O51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="P51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Q51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="R51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="S51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="T51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="U51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="V51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="W51" s="15" t="str">
+      <c r="G51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="H51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="I51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="J51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="K51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="L51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="M51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="N51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="O51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="P51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="R51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="S51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="T51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="U51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="V51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="W51" s="13" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="X51" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Y51" s="15" t="str">
+      <c r="X51" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Y51" s="13" t="str">
         <v>目录名 gpt-5.2-chat</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="str">
+      <c r="A52" s="13" t="str">
         <v>gpt-5.3-chat-latest</v>
       </c>
-      <c r="B52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="C52" s="15" t="str">
+      <c r="B52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="C52" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="D52" s="15" t="str">
+      <c r="D52" s="13" t="str">
         <v>GPT</v>
       </c>
-      <c r="E52" s="15" t="str">
+      <c r="E52" s="13" t="str">
         <v>标准价</v>
       </c>
-      <c r="F52" s="15" t="str">
+      <c r="F52" s="13" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
-      <c r="G52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="H52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="I52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="J52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="K52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="L52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="M52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="N52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="O52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="P52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Q52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="R52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="S52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="T52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="U52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="V52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="W52" s="15" t="str">
+      <c r="G52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="H52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="I52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="J52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="K52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="L52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="M52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="N52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="O52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="P52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Q52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="R52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="S52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="T52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="U52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="V52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="W52" s="13" t="str">
         <v>— 未接入</v>
       </c>
-      <c r="X52" s="15" t="str">
-        <v>—</v>
-      </c>
-      <c r="Y52" s="15" t="str">
+      <c r="X52" s="13" t="str">
+        <v>—</v>
+      </c>
+      <c r="Y52" s="13" t="str">
         <v>目录名 gpt-5.3-chat</v>
       </c>
     </row>
@@ -5370,13 +5370,13 @@
         <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="L59" s="19" t="str">
-        <v>入 $0.6 · 出 $2.4 · 缓 $0.12</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="M59" s="19" t="str">
-        <v>入 +85.7% / 出 +85.7%</v>
+        <v>入 -7.1% / 出 -7.1%</v>
       </c>
       <c r="N59" s="19" t="str">
-        <v>入 $0.6 · 出 $2.4 · 缓 $0.12</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="O59" s="19" t="str">
         <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
@@ -5438,7 +5438,7 @@
         <v>—</v>
       </c>
       <c r="I60" s="19" t="str">
-        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
       <c r="J60" s="19" t="str">
         <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
@@ -5447,25 +5447,25 @@
         <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="L60" s="19" t="str">
-        <v>入 $0.6 · 出 $2.4 · 缓 $0.12</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="M60" s="19" t="str">
-        <v>入 +85.7% / 出 +85.7%</v>
+        <v>入 -7.1% / 出 -7.1%</v>
       </c>
       <c r="N60" s="19" t="str">
-        <v>入 $0.6 · 出 $2.4 · 缓 $0.12</v>
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
       </c>
       <c r="O60" s="19" t="str">
-        <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
       <c r="P60" s="19" t="str">
-        <v>0%</v>
+        <v>-50%</v>
       </c>
       <c r="Q60" s="19" t="str">
-        <v>0%</v>
+        <v>-50%</v>
       </c>
       <c r="R60" s="19" t="str">
-        <v>0%</v>
+        <v>-50%</v>
       </c>
       <c r="S60" s="19" t="str">
         <v>—</v>
@@ -5474,13 +5474,13 @@
         <v>—</v>
       </c>
       <c r="U60" s="19" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-50% 出⚠-50% 缓⚠-50%</v>
       </c>
       <c r="V60" s="19" t="str">
         <v>入⚠-53.6% 出⚠-53.6% 缓⚠-53.6%</v>
       </c>
       <c r="W60" s="19" t="str">
-        <v>入✅ 出✅ 缓✅</v>
+        <v>入⚠-50% 出⚠-50% 缓⚠-50%</v>
       </c>
       <c r="X60" s="19" t="str">
         <v>intl</v>
@@ -10026,7 +10026,7 @@
     <col min="5" max="5" width="32.83203125" customWidth="1"/>
     <col min="6" max="6" width="32.83203125" customWidth="1"/>
     <col min="7" max="7" width="44.83203125" customWidth="1"/>
-    <col min="8" max="8" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10282,13 +10282,13 @@
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="G9" s="5" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="H9" s="5" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I9" s="5" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 出-33.3% 缓-37.1%</v>
       </c>
     </row>
     <row r="10">
@@ -10311,13 +10311,13 @@
         <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="G10" s="5" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="H10" s="5" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I10" s="5" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 出-33.3% 缓-75%</v>
       </c>
     </row>
     <row r="11">
@@ -11616,13 +11616,13 @@
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="G55" s="5" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="H55" s="5" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I55" s="5" t="str">
-        <v>✅ 一致</v>
+        <v>—</v>
       </c>
     </row>
     <row r="56">
@@ -11645,13 +11645,13 @@
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="G56" s="5" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>—</v>
       </c>
       <c r="H56" s="5" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I56" s="5" t="str">
-        <v>✅ 一致</v>
+        <v>—</v>
       </c>
     </row>
     <row r="57">
@@ -13002,7 +13002,7 @@
         <v>输入&gt;512k</v>
       </c>
       <c r="E103" s="5" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="F103" s="5" t="str">
         <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
@@ -13011,7 +13011,7 @@
         <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
       </c>
       <c r="H103" s="5" t="str">
-        <v>⚠ 入+100% 出+100% 缓+100%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="I103" s="5" t="str">
         <v>✅ 一致</v>
@@ -13736,7 +13736,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K52"/>
   <cols>
     <col min="1" max="1" width="56.83203125" customWidth="1"/>
     <col min="2" max="2" width="19.83203125" customWidth="1"/>
@@ -13794,31 +13794,31 @@
         <v>23</v>
       </c>
       <c r="C2" s="21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="21">
         <v>0</v>
       </c>
       <c r="F2" s="21">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" s="21" t="str">
-        <v>+100% ~ +3900%</v>
+        <v>+900% ~ +3900%</v>
       </c>
       <c r="J2" s="21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" s="21" t="str">
-        <v>deepseek-v4-flash(+900%)；deepseek-v4-pro(+3900%)；minimax-m3(+100%)</v>
+        <v>deepseek-v4-flash(+900%)；deepseek-v4-pro(+3900%)</v>
       </c>
     </row>
     <row r="3">
@@ -13896,10 +13896,10 @@
         <v>AIGC国内站</v>
       </c>
       <c r="B5" s="21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="21">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" s="21">
         <v>9</v>
@@ -13908,10 +13908,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="21">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G5" s="21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H5" s="21">
         <v>11</v>
@@ -13931,10 +13931,10 @@
         <v>AIGC国际站</v>
       </c>
       <c r="B6" s="21">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="21">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" s="21">
         <v>6</v>
@@ -13943,10 +13943,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G6" s="21">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H6" s="21">
         <v>6</v>
@@ -14001,10 +14001,10 @@
         <v>网聚云联云门户</v>
       </c>
       <c r="B8" s="21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="21">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="21">
         <v>0</v>
@@ -14013,10 +14013,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G8" s="21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H8" s="21">
         <v>0</v>
@@ -14036,34 +14036,34 @@
         <v>中转站-cust</v>
       </c>
       <c r="B9" s="21">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" s="21">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="21">
         <v>0</v>
       </c>
       <c r="F9" s="21">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G9" s="21">
         <v>88</v>
       </c>
       <c r="H9" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="21" t="str">
-        <v>+100%</v>
+        <v>—</v>
       </c>
       <c r="J9" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="21" t="str">
-        <v>minimax-m3(+100%)</v>
+        <v>—</v>
       </c>
     </row>
     <row r="10">
@@ -14243,22 +14243,22 @@
     </row>
     <row r="15">
       <c r="A15" s="21" t="str">
-        <v>TokenHub广州</v>
+        <v>百炼北京</v>
       </c>
       <c r="B15" s="21" t="str">
-        <v>minimax-m3</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C15" s="21" t="str">
-        <v>MiniMax M3</v>
+        <v>DeepSeek V4 Flash Direct</v>
       </c>
       <c r="D15" s="21" t="str">
-        <v>512k&lt;输入</v>
+        <v>统一价</v>
       </c>
       <c r="E15" s="21" t="str">
-        <v>+100%</v>
+        <v>+900%</v>
       </c>
       <c r="F15" s="21" t="str">
-        <v>⚠ 入+100% 出+100% 缓+100%</v>
+        <v>⚠ 缓+900%</v>
       </c>
       <c r="G15" s="21" t="str">
         <v/>
@@ -14281,19 +14281,19 @@
         <v>百炼北京</v>
       </c>
       <c r="B16" s="21" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C16" s="21" t="str">
-        <v>DeepSeek V4 Flash Direct</v>
+        <v>DeepSeek V4 Pro Direct</v>
       </c>
       <c r="D16" s="21" t="str">
         <v>统一价</v>
       </c>
       <c r="E16" s="21" t="str">
-        <v>+900%</v>
+        <v>+300%</v>
       </c>
       <c r="F16" s="21" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 入+300% 出+300%</v>
       </c>
       <c r="G16" s="21" t="str">
         <v/>
@@ -14316,19 +14316,19 @@
         <v>百炼北京</v>
       </c>
       <c r="B17" s="21" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>glm-5</v>
       </c>
       <c r="C17" s="21" t="str">
-        <v>DeepSeek V4 Pro Direct</v>
+        <v>GLM 5</v>
       </c>
       <c r="D17" s="21" t="str">
-        <v>统一价</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E17" s="21" t="str">
-        <v>+300%</v>
+        <v>+20%</v>
       </c>
       <c r="F17" s="21" t="str">
-        <v>⚠ 入+300% 出+300%</v>
+        <v>⚠ 缓-20%</v>
       </c>
       <c r="G17" s="21" t="str">
         <v/>
@@ -14348,16 +14348,16 @@
     </row>
     <row r="18">
       <c r="A18" s="21" t="str">
-        <v>百炼北京</v>
+        <v/>
       </c>
       <c r="B18" s="21" t="str">
-        <v>glm-5</v>
+        <v/>
       </c>
       <c r="C18" s="21" t="str">
-        <v>GLM 5</v>
+        <v/>
       </c>
       <c r="D18" s="21" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="E18" s="21" t="str">
         <v>+20%</v>
@@ -14383,22 +14383,22 @@
     </row>
     <row r="19">
       <c r="A19" s="21" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B19" s="21" t="str">
-        <v/>
+        <v>glm-5.1</v>
       </c>
       <c r="C19" s="21" t="str">
-        <v/>
+        <v>GLM-5.1</v>
       </c>
       <c r="D19" s="21" t="str">
-        <v>32k&lt;=输入</v>
+        <v>0&lt;=输入&lt;32k</v>
       </c>
       <c r="E19" s="21" t="str">
-        <v>+20%</v>
+        <v>+7.7%</v>
       </c>
       <c r="F19" s="21" t="str">
-        <v>⚠ 缓-20%</v>
+        <v>⚠ 缓-7.7%</v>
       </c>
       <c r="G19" s="21" t="str">
         <v/>
@@ -14418,22 +14418,22 @@
     </row>
     <row r="20">
       <c r="A20" s="21" t="str">
-        <v>百炼北京</v>
+        <v/>
       </c>
       <c r="B20" s="21" t="str">
-        <v>glm-5.1</v>
+        <v/>
       </c>
       <c r="C20" s="21" t="str">
-        <v>GLM-5.1</v>
+        <v/>
       </c>
       <c r="D20" s="21" t="str">
-        <v>0&lt;=输入&lt;32k</v>
+        <v>32k&lt;=输入</v>
       </c>
       <c r="E20" s="21" t="str">
-        <v>+7.7%</v>
+        <v>+20%</v>
       </c>
       <c r="F20" s="21" t="str">
-        <v>⚠ 缓-7.7%</v>
+        <v>⚠ 缓-20%</v>
       </c>
       <c r="G20" s="21" t="str">
         <v/>
@@ -14453,22 +14453,22 @@
     </row>
     <row r="21">
       <c r="A21" s="21" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B21" s="21" t="str">
-        <v/>
+        <v>qwen3.5-flash</v>
       </c>
       <c r="C21" s="21" t="str">
-        <v/>
+        <v>Qwen3.5 Flash</v>
       </c>
       <c r="D21" s="21" t="str">
-        <v>32k&lt;=输入</v>
+        <v>0&lt;输入&lt;=128k</v>
       </c>
       <c r="E21" s="21" t="str">
-        <v>+20%</v>
+        <v>+100%</v>
       </c>
       <c r="F21" s="21" t="str">
-        <v>⚠ 缓-20%</v>
+        <v>⚠ 缓+100%</v>
       </c>
       <c r="G21" s="21" t="str">
         <v/>
@@ -14488,16 +14488,16 @@
     </row>
     <row r="22">
       <c r="A22" s="21" t="str">
-        <v>百炼北京</v>
+        <v/>
       </c>
       <c r="B22" s="21" t="str">
-        <v>qwen3.5-flash</v>
+        <v/>
       </c>
       <c r="C22" s="21" t="str">
-        <v>Qwen3.5 Flash</v>
+        <v/>
       </c>
       <c r="D22" s="21" t="str">
-        <v>0&lt;输入&lt;=128k</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E22" s="21" t="str">
         <v>+100%</v>
@@ -14532,7 +14532,7 @@
         <v/>
       </c>
       <c r="D23" s="21" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E23" s="21" t="str">
         <v>+100%</v>
@@ -14558,16 +14558,16 @@
     </row>
     <row r="24">
       <c r="A24" s="21" t="str">
-        <v/>
+        <v>百炼北京</v>
       </c>
       <c r="B24" s="21" t="str">
-        <v/>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="C24" s="21" t="str">
-        <v/>
+        <v>Qwen3.5 Plus</v>
       </c>
       <c r="D24" s="21" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>输入&lt;=128k</v>
       </c>
       <c r="E24" s="21" t="str">
         <v>+100%</v>
@@ -14593,16 +14593,16 @@
     </row>
     <row r="25">
       <c r="A25" s="21" t="str">
-        <v>百炼北京</v>
+        <v/>
       </c>
       <c r="B25" s="21" t="str">
-        <v>qwen3.5-plus</v>
+        <v/>
       </c>
       <c r="C25" s="21" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v/>
       </c>
       <c r="D25" s="21" t="str">
-        <v>输入&lt;=128k</v>
+        <v>128k&lt;输入&lt;=256k</v>
       </c>
       <c r="E25" s="21" t="str">
         <v>+100%</v>
@@ -14637,7 +14637,7 @@
         <v/>
       </c>
       <c r="D26" s="21" t="str">
-        <v>128k&lt;输入&lt;=256k</v>
+        <v>256k&lt;输入&lt;=1M</v>
       </c>
       <c r="E26" s="21" t="str">
         <v>+100%</v>
@@ -14663,22 +14663,22 @@
     </row>
     <row r="27">
       <c r="A27" s="21" t="str">
-        <v/>
+        <v>百炼国际</v>
       </c>
       <c r="B27" s="21" t="str">
-        <v/>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="C27" s="21" t="str">
-        <v/>
+        <v>DeepSeek V3.2</v>
       </c>
       <c r="D27" s="21" t="str">
-        <v>256k&lt;输入&lt;=1M</v>
+        <v>统一价</v>
       </c>
       <c r="E27" s="21" t="str">
-        <v>+100%</v>
+        <v>+270.5%</v>
       </c>
       <c r="F27" s="21" t="str">
-        <v>⚠ 缓+100%</v>
+        <v>⚠ 入+85.2% 出+270.5% 缓+85.2%</v>
       </c>
       <c r="G27" s="21" t="str">
         <v/>
@@ -14701,19 +14701,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B28" s="21" t="str">
-        <v>deepseek-v3.2</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C28" s="21" t="str">
-        <v>DeepSeek V3.2</v>
+        <v>DeepSeek V4 Flash Direct</v>
       </c>
       <c r="D28" s="21" t="str">
         <v>统一价</v>
       </c>
       <c r="E28" s="21" t="str">
-        <v>+270.5%</v>
+        <v>+1200%</v>
       </c>
       <c r="F28" s="21" t="str">
-        <v>⚠ 入+85.2% 出+270.5% 缓+85.2%</v>
+        <v>⚠ 入+30% 出+30% 缓+1200%</v>
       </c>
       <c r="G28" s="21" t="str">
         <v/>
@@ -14736,19 +14736,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B29" s="21" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C29" s="21" t="str">
-        <v>DeepSeek V4 Flash Direct</v>
+        <v>DeepSeek V4 Pro Direct</v>
       </c>
       <c r="D29" s="21" t="str">
         <v>统一价</v>
       </c>
       <c r="E29" s="21" t="str">
-        <v>+1200%</v>
+        <v>+5100%</v>
       </c>
       <c r="F29" s="21" t="str">
-        <v>⚠ 入+30% 出+30% 缓+1200%</v>
+        <v>⚠ 入+420% 出+420% 缓+5100%</v>
       </c>
       <c r="G29" s="21" t="str">
         <v/>
@@ -14771,19 +14771,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B30" s="21" t="str">
-        <v>deepseek-v4-pro</v>
+        <v>glm-5.2</v>
       </c>
       <c r="C30" s="21" t="str">
-        <v>DeepSeek V4 Pro Direct</v>
+        <v>GLM-5.2</v>
       </c>
       <c r="D30" s="21" t="str">
         <v>统一价</v>
       </c>
       <c r="E30" s="21" t="str">
-        <v>+5100%</v>
+        <v>+13.7%</v>
       </c>
       <c r="F30" s="21" t="str">
-        <v>⚠ 入+420% 出+420% 缓+5100%</v>
+        <v>⚠ 入+13.7% 出+2.1% 缓-9%</v>
       </c>
       <c r="G30" s="21" t="str">
         <v/>
@@ -14806,19 +14806,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B31" s="21" t="str">
-        <v>glm-5.2</v>
+        <v>qwen-flash</v>
       </c>
       <c r="C31" s="21" t="str">
-        <v>GLM-5.2</v>
+        <v>Qwen Flash</v>
       </c>
       <c r="D31" s="21" t="str">
-        <v>统一价</v>
+        <v>0&lt;Token≤256K</v>
       </c>
       <c r="E31" s="21" t="str">
-        <v>+13.7%</v>
+        <v>+116.7%</v>
       </c>
       <c r="F31" s="21" t="str">
-        <v>⚠ 入+13.7% 出+2.1% 缓-9%</v>
+        <v>⚠ 入+116.7% 出+73.3% 缓+116.7%</v>
       </c>
       <c r="G31" s="21" t="str">
         <v/>
@@ -14841,19 +14841,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B32" s="21" t="str">
-        <v>qwen-flash</v>
+        <v>qwen-max</v>
       </c>
       <c r="C32" s="21" t="str">
-        <v>Qwen Flash</v>
+        <v>Qwen Max</v>
       </c>
       <c r="D32" s="21" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>无阶梯计价</v>
       </c>
       <c r="E32" s="21" t="str">
-        <v>+116.7%</v>
+        <v>+333.3%</v>
       </c>
       <c r="F32" s="21" t="str">
-        <v>⚠ 入+116.7% 出+73.3% 缓+116.7%</v>
+        <v>⚠ 入+333.3% 出+333.3%</v>
       </c>
       <c r="G32" s="21" t="str">
         <v/>
@@ -14876,19 +14876,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B33" s="21" t="str">
-        <v>qwen-max</v>
+        <v>qwen-turbo</v>
       </c>
       <c r="C33" s="21" t="str">
-        <v>Qwen Max</v>
+        <v>Qwen Turbo</v>
       </c>
       <c r="D33" s="21" t="str">
-        <v>无阶梯计价</v>
+        <v>统一价</v>
       </c>
       <c r="E33" s="21" t="str">
-        <v>+333.3%</v>
+        <v>+116.7%</v>
       </c>
       <c r="F33" s="21" t="str">
-        <v>⚠ 入+333.3% 出+333.3%</v>
+        <v>⚠ 入+8.3% 出+116.7%</v>
       </c>
       <c r="G33" s="21" t="str">
         <v/>
@@ -14911,19 +14911,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B34" s="21" t="str">
-        <v>qwen-turbo</v>
+        <v>qwen3.5-plus</v>
       </c>
       <c r="C34" s="21" t="str">
-        <v>Qwen Turbo</v>
+        <v>Qwen3.5 Plus</v>
       </c>
       <c r="D34" s="21" t="str">
-        <v>统一价</v>
+        <v>0&lt;Token≤256K</v>
       </c>
       <c r="E34" s="21" t="str">
-        <v>+116.7%</v>
+        <v>+30%</v>
       </c>
       <c r="F34" s="21" t="str">
-        <v>⚠ 入+8.3% 出+116.7%</v>
+        <v>⚠ 入+30% 出+30%</v>
       </c>
       <c r="G34" s="21" t="str">
         <v/>
@@ -14946,19 +14946,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B35" s="21" t="str">
-        <v>qwen3.5-plus</v>
+        <v>qwen3.6-flash</v>
       </c>
       <c r="C35" s="21" t="str">
-        <v>Qwen3.5 Plus</v>
+        <v>Qwen3.6 Flash</v>
       </c>
       <c r="D35" s="21" t="str">
         <v>0&lt;Token≤256K</v>
       </c>
       <c r="E35" s="21" t="str">
-        <v>+30%</v>
+        <v>+35.4%</v>
       </c>
       <c r="F35" s="21" t="str">
-        <v>⚠ 入+30% 出+30%</v>
+        <v>⚠ 入+35.4% 出+35.4%</v>
       </c>
       <c r="G35" s="21" t="str">
         <v/>
@@ -14981,19 +14981,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B36" s="21" t="str">
-        <v>qwen3.6-flash</v>
+        <v>qwen3.6-plus</v>
       </c>
       <c r="C36" s="21" t="str">
-        <v>Qwen3.6 Flash</v>
+        <v>Qwen3.6 Plus</v>
       </c>
       <c r="D36" s="21" t="str">
         <v>0&lt;Token≤256K</v>
       </c>
       <c r="E36" s="21" t="str">
-        <v>+35.4%</v>
+        <v>+62.5%</v>
       </c>
       <c r="F36" s="21" t="str">
-        <v>⚠ 入+35.4% 出+35.4%</v>
+        <v>⚠ 入+62.5% 出+62.5%</v>
       </c>
       <c r="G36" s="21" t="str">
         <v/>
@@ -15016,19 +15016,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B37" s="21" t="str">
-        <v>qwen3.6-plus</v>
+        <v>qwen3.7-plus</v>
       </c>
       <c r="C37" s="21" t="str">
-        <v>Qwen3.6 Plus</v>
+        <v>Qwen3.7 Plus</v>
       </c>
       <c r="D37" s="21" t="str">
         <v>0&lt;Token≤256K</v>
       </c>
       <c r="E37" s="21" t="str">
-        <v>+62.5%</v>
+        <v>+30%</v>
       </c>
       <c r="F37" s="21" t="str">
-        <v>⚠ 入+62.5% 出+62.5%</v>
+        <v>⚠ 入+30% 出+30% 缓+30%</v>
       </c>
       <c r="G37" s="21" t="str">
         <v/>
@@ -15048,22 +15048,22 @@
     </row>
     <row r="38">
       <c r="A38" s="21" t="str">
-        <v>百炼国际</v>
+        <v>火山方舟</v>
       </c>
       <c r="B38" s="21" t="str">
-        <v>qwen3.7-plus</v>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="C38" s="21" t="str">
-        <v>Qwen3.7 Plus</v>
+        <v>DeepSeek V3.2</v>
       </c>
       <c r="D38" s="21" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v>输入(32k,128k]</v>
       </c>
       <c r="E38" s="21" t="str">
-        <v>+30%</v>
+        <v>+100%</v>
       </c>
       <c r="F38" s="21" t="str">
-        <v>⚠ 入+30% 出+30% 缓+30%</v>
+        <v>⚠ 入+100% 出+100%</v>
       </c>
       <c r="G38" s="21" t="str">
         <v/>
@@ -15086,19 +15086,19 @@
         <v>火山方舟</v>
       </c>
       <c r="B39" s="21" t="str">
-        <v>deepseek-v3.2</v>
+        <v>deepseek-v4-flash</v>
       </c>
       <c r="C39" s="21" t="str">
-        <v>DeepSeek V3.2</v>
+        <v>DeepSeek V4 Flash Direct</v>
       </c>
       <c r="D39" s="21" t="str">
-        <v>输入(32k,128k]</v>
+        <v>统一价</v>
       </c>
       <c r="E39" s="21" t="str">
-        <v>+100%</v>
+        <v>+900%</v>
       </c>
       <c r="F39" s="21" t="str">
-        <v>⚠ 入+100% 出+100%</v>
+        <v>⚠ 缓+900%</v>
       </c>
       <c r="G39" s="21" t="str">
         <v/>
@@ -15121,19 +15121,19 @@
         <v>火山方舟</v>
       </c>
       <c r="B40" s="21" t="str">
-        <v>deepseek-v4-flash</v>
+        <v>deepseek-v4-pro</v>
       </c>
       <c r="C40" s="21" t="str">
-        <v>DeepSeek V4 Flash Direct</v>
+        <v>DeepSeek V4 Pro Direct</v>
       </c>
       <c r="D40" s="21" t="str">
         <v>统一价</v>
       </c>
       <c r="E40" s="21" t="str">
-        <v>+900%</v>
+        <v>+3900%</v>
       </c>
       <c r="F40" s="21" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
       <c r="G40" s="21" t="str">
         <v/>
@@ -15153,22 +15153,22 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="str">
-        <v>火山方舟</v>
+        <v/>
       </c>
       <c r="B41" s="21" t="str">
-        <v>deepseek-v4-pro</v>
+        <v/>
       </c>
       <c r="C41" s="21" t="str">
-        <v>DeepSeek V4 Pro Direct</v>
+        <v/>
       </c>
       <c r="D41" s="21" t="str">
-        <v>统一价</v>
+        <v/>
       </c>
       <c r="E41" s="21" t="str">
-        <v>+3900%</v>
+        <v/>
       </c>
       <c r="F41" s="21" t="str">
-        <v>⚠ 入+300% 出+300% 缓+3900%</v>
+        <v/>
       </c>
       <c r="G41" s="21" t="str">
         <v/>
@@ -15188,22 +15188,22 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="str">
-        <v>中转站-cust</v>
+        <v>—— 偏差≥50% · 待核验（未登记例外）——</v>
       </c>
       <c r="B42" s="21" t="str">
-        <v>minimax-m3</v>
+        <v/>
       </c>
       <c r="C42" s="21" t="str">
-        <v>MiniMax M3</v>
+        <v/>
       </c>
       <c r="D42" s="21" t="str">
-        <v>512k&lt;输入</v>
+        <v/>
       </c>
       <c r="E42" s="21" t="str">
-        <v>+100%</v>
+        <v/>
       </c>
       <c r="F42" s="21" t="str">
-        <v>⚠ 入+100% 出+100% 缓+100%</v>
+        <v/>
       </c>
       <c r="G42" s="21" t="str">
         <v/>
@@ -15223,22 +15223,22 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="str">
-        <v/>
+        <v>供应商</v>
       </c>
       <c r="B43" s="21" t="str">
-        <v/>
+        <v>Trinity ID</v>
       </c>
       <c r="C43" s="21" t="str">
-        <v/>
+        <v>显示名</v>
       </c>
       <c r="D43" s="21" t="str">
-        <v/>
+        <v>档位</v>
       </c>
       <c r="E43" s="21" t="str">
-        <v/>
+        <v>偏差%</v>
       </c>
       <c r="F43" s="21" t="str">
-        <v/>
+        <v>供应商vs官方</v>
       </c>
       <c r="G43" s="21" t="str">
         <v/>
@@ -15258,22 +15258,22 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="str">
-        <v>—— 偏差≥50% · 待核验（未登记例外）——</v>
+        <v>百炼国际</v>
       </c>
       <c r="B44" s="21" t="str">
-        <v/>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="C44" s="21" t="str">
-        <v/>
+        <v>DeepSeek V3.2</v>
       </c>
       <c r="D44" s="21" t="str">
-        <v/>
+        <v>统一价</v>
       </c>
       <c r="E44" s="21" t="str">
-        <v/>
+        <v>+270.5%</v>
       </c>
       <c r="F44" s="21" t="str">
-        <v/>
+        <v>⚠ 入+85.2% 出+270.5% 缓+85.2%</v>
       </c>
       <c r="G44" s="21" t="str">
         <v/>
@@ -15293,22 +15293,22 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
-        <v>供应商</v>
+        <v>百炼国际</v>
       </c>
       <c r="B45" s="21" t="str">
-        <v>Trinity ID</v>
+        <v>qwen-flash</v>
       </c>
       <c r="C45" s="21" t="str">
-        <v>显示名</v>
+        <v>Qwen Flash</v>
       </c>
       <c r="D45" s="21" t="str">
-        <v>档位</v>
+        <v>0&lt;Token≤256K</v>
       </c>
       <c r="E45" s="21" t="str">
-        <v>偏差%</v>
+        <v>+116.7%</v>
       </c>
       <c r="F45" s="21" t="str">
-        <v>供应商vs官方</v>
+        <v>⚠ 入+116.7% 出+73.3% 缓+116.7%</v>
       </c>
       <c r="G45" s="21" t="str">
         <v/>
@@ -15328,22 +15328,22 @@
     </row>
     <row r="46">
       <c r="A46" s="21" t="str">
-        <v>TokenHub广州</v>
+        <v>百炼国际</v>
       </c>
       <c r="B46" s="21" t="str">
-        <v>minimax-m3</v>
+        <v>qwen-max</v>
       </c>
       <c r="C46" s="21" t="str">
-        <v>MiniMax M3</v>
+        <v>Qwen Max</v>
       </c>
       <c r="D46" s="21" t="str">
-        <v>512k&lt;输入</v>
+        <v>无阶梯计价</v>
       </c>
       <c r="E46" s="21" t="str">
-        <v>+100%</v>
+        <v>+333.3%</v>
       </c>
       <c r="F46" s="21" t="str">
-        <v>⚠ 入+100% 出+100% 缓+100%</v>
+        <v>⚠ 入+333.3% 出+333.3%</v>
       </c>
       <c r="G46" s="21" t="str">
         <v/>
@@ -15366,19 +15366,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B47" s="21" t="str">
-        <v>deepseek-v3.2</v>
+        <v>qwen-turbo</v>
       </c>
       <c r="C47" s="21" t="str">
-        <v>DeepSeek V3.2</v>
+        <v>Qwen Turbo</v>
       </c>
       <c r="D47" s="21" t="str">
         <v>统一价</v>
       </c>
       <c r="E47" s="21" t="str">
-        <v>+270.5%</v>
+        <v>+116.7%</v>
       </c>
       <c r="F47" s="21" t="str">
-        <v>⚠ 入+85.2% 出+270.5% 缓+85.2%</v>
+        <v>⚠ 入+8.3% 出+116.7%</v>
       </c>
       <c r="G47" s="21" t="str">
         <v/>
@@ -15401,19 +15401,19 @@
         <v>百炼国际</v>
       </c>
       <c r="B48" s="21" t="str">
-        <v>qwen-flash</v>
+        <v>qwen3.6-plus</v>
       </c>
       <c r="C48" s="21" t="str">
-        <v>Qwen Flash</v>
+        <v>Qwen3.6 Plus</v>
       </c>
       <c r="D48" s="21" t="str">
         <v>0&lt;Token≤256K</v>
       </c>
       <c r="E48" s="21" t="str">
-        <v>+116.7%</v>
+        <v>+62.5%</v>
       </c>
       <c r="F48" s="21" t="str">
-        <v>⚠ 入+116.7% 出+73.3% 缓+116.7%</v>
+        <v>⚠ 入+62.5% 出+62.5%</v>
       </c>
       <c r="G48" s="21" t="str">
         <v/>
@@ -15433,22 +15433,22 @@
     </row>
     <row r="49">
       <c r="A49" s="21" t="str">
-        <v>百炼国际</v>
+        <v>火山方舟</v>
       </c>
       <c r="B49" s="21" t="str">
-        <v>qwen-max</v>
+        <v>deepseek-v3.2</v>
       </c>
       <c r="C49" s="21" t="str">
-        <v>Qwen Max</v>
+        <v>DeepSeek V3.2</v>
       </c>
       <c r="D49" s="21" t="str">
-        <v>无阶梯计价</v>
+        <v>输入(32k,128k]</v>
       </c>
       <c r="E49" s="21" t="str">
-        <v>+333.3%</v>
+        <v>+100%</v>
       </c>
       <c r="F49" s="21" t="str">
-        <v>⚠ 入+333.3% 出+333.3%</v>
+        <v>⚠ 入+100% 出+100%</v>
       </c>
       <c r="G49" s="21" t="str">
         <v/>
@@ -15468,22 +15468,22 @@
     </row>
     <row r="50">
       <c r="A50" s="21" t="str">
-        <v>百炼国际</v>
+        <v/>
       </c>
       <c r="B50" s="21" t="str">
-        <v>qwen-turbo</v>
+        <v/>
       </c>
       <c r="C50" s="21" t="str">
-        <v>Qwen Turbo</v>
+        <v/>
       </c>
       <c r="D50" s="21" t="str">
-        <v>统一价</v>
+        <v/>
       </c>
       <c r="E50" s="21" t="str">
-        <v>+116.7%</v>
+        <v/>
       </c>
       <c r="F50" s="21" t="str">
-        <v>⚠ 入+8.3% 出+116.7%</v>
+        <v/>
       </c>
       <c r="G50" s="21" t="str">
         <v/>
@@ -15503,22 +15503,22 @@
     </row>
     <row r="51">
       <c r="A51" s="21" t="str">
-        <v>百炼国际</v>
+        <v>生成时间：2026-08-18T07:43:17Z</v>
       </c>
       <c r="B51" s="21" t="str">
-        <v>qwen3.6-plus</v>
+        <v/>
       </c>
       <c r="C51" s="21" t="str">
-        <v>Qwen3.6 Plus</v>
+        <v/>
       </c>
       <c r="D51" s="21" t="str">
-        <v>0&lt;Token≤256K</v>
+        <v/>
       </c>
       <c r="E51" s="21" t="str">
-        <v>+62.5%</v>
+        <v/>
       </c>
       <c r="F51" s="21" t="str">
-        <v>⚠ 入+62.5% 出+62.5%</v>
+        <v/>
       </c>
       <c r="G51" s="21" t="str">
         <v/>
@@ -15538,22 +15538,22 @@
     </row>
     <row r="52">
       <c r="A52" s="21" t="str">
-        <v>火山方舟</v>
+        <v>说明：一致=与厂商官方价偏差&lt;0.5%；≥50%且未登记例外标「待核验」须人工复核；模型级不一致=任一档位不一致</v>
       </c>
       <c r="B52" s="21" t="str">
-        <v>deepseek-v3.2</v>
+        <v/>
       </c>
       <c r="C52" s="21" t="str">
-        <v>DeepSeek V3.2</v>
+        <v/>
       </c>
       <c r="D52" s="21" t="str">
-        <v>输入(32k,128k]</v>
+        <v/>
       </c>
       <c r="E52" s="21" t="str">
-        <v>+100%</v>
+        <v/>
       </c>
       <c r="F52" s="21" t="str">
-        <v>⚠ 入+100% 出+100%</v>
+        <v/>
       </c>
       <c r="G52" s="21" t="str">
         <v/>
@@ -15568,152 +15568,12 @@
         <v/>
       </c>
       <c r="K52" s="21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="21" t="str">
-        <v>中转站-cust</v>
-      </c>
-      <c r="B53" s="21" t="str">
-        <v>minimax-m3</v>
-      </c>
-      <c r="C53" s="21" t="str">
-        <v>MiniMax M3</v>
-      </c>
-      <c r="D53" s="21" t="str">
-        <v>512k&lt;输入</v>
-      </c>
-      <c r="E53" s="21" t="str">
-        <v>+100%</v>
-      </c>
-      <c r="F53" s="21" t="str">
-        <v>⚠ 入+100% 出+100% 缓+100%</v>
-      </c>
-      <c r="G53" s="21" t="str">
-        <v/>
-      </c>
-      <c r="H53" s="21" t="str">
-        <v/>
-      </c>
-      <c r="I53" s="21" t="str">
-        <v/>
-      </c>
-      <c r="J53" s="21" t="str">
-        <v/>
-      </c>
-      <c r="K53" s="21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="B54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="C54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="D54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="E54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="F54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="G54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="H54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="I54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="J54" s="21" t="str">
-        <v/>
-      </c>
-      <c r="K54" s="21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="21" t="str">
-        <v>生成时间：2026-08-09T04:32:45Z</v>
-      </c>
-      <c r="B55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="C55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="D55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="E55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="F55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="G55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="H55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="I55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="J55" s="21" t="str">
-        <v/>
-      </c>
-      <c r="K55" s="21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="str">
-        <v>说明：一致=与厂商官方价偏差&lt;0.5%；≥50%且未登记例外标「待核验」须人工复核；模型级不一致=任一档位不一致</v>
-      </c>
-      <c r="B56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="C56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="D56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="E56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="F56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="G56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="H56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="I56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="J56" s="21" t="str">
-        <v/>
-      </c>
-      <c r="K56" s="21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K52"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15726,11 +15586,11 @@
     <col min="2" max="2" width="31.83203125" customWidth="1"/>
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="31.83203125" customWidth="1"/>
     <col min="6" max="6" width="31.83203125" customWidth="1"/>
     <col min="7" max="7" width="44.83203125" customWidth="1"/>
     <col min="8" max="8" width="29.83203125" customWidth="1"/>
-    <col min="9" max="9" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16797,13 +16657,13 @@
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
       </c>
       <c r="G37" s="13" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="H37" s="13" t="str">
         <v>⚠ 缓+900%</v>
       </c>
       <c r="I37" s="13" t="str">
-        <v>⚠ 入-13.3% 出-13.3% 缓+766.6%</v>
+        <v>⚠ 入-69.7% 出-79.8% 缓+90.5%</v>
       </c>
     </row>
     <row r="38">
@@ -16826,13 +16686,13 @@
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="G38" s="13" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="H38" s="13" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I38" s="13" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 出-33.3% 缓-37.1%</v>
       </c>
     </row>
     <row r="39">
@@ -16855,13 +16715,13 @@
         <v>入 ¥12 · 出 ¥24 · 缓 ¥1</v>
       </c>
       <c r="G39" s="13" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="H39" s="13" t="str">
         <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
       <c r="I39" s="13" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 出-33.3% 缓+150%</v>
       </c>
     </row>
     <row r="40">
@@ -16884,13 +16744,13 @@
         <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="G40" s="13" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="H40" s="13" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I40" s="13" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 出-33.3% 缓-75%</v>
       </c>
     </row>
     <row r="41">
@@ -16994,7 +16854,7 @@
         <v>512k&lt;输入</v>
       </c>
       <c r="E44" s="15" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+        <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
       </c>
       <c r="F44" s="15" t="str">
         <v>入 ¥4.2 · 出 ¥16.8 · 缓 ¥0.84</v>
@@ -17003,7 +16863,7 @@
         <v>入 $0.646154 · 出 $2.584615 · 缓 $0.129231</v>
       </c>
       <c r="H44" s="15" t="str">
-        <v>⚠ 入+100% 出+100% 缓+100%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="I44" s="15" t="str">
         <v>✅ 一致</v>
@@ -17060,7 +16920,7 @@
     <col min="6" max="6" width="36.83203125" customWidth="1"/>
     <col min="7" max="7" width="44.83203125" customWidth="1"/>
     <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18069,13 +17929,13 @@
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
       </c>
       <c r="G35" s="11" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="H35" s="11" t="str">
         <v>⚠ 缓+900%</v>
       </c>
       <c r="I35" s="11" t="str">
-        <v>⚠ 入-13.3% 出-13.3% 缓+766.6%</v>
+        <v>⚠ 入-69.7% 出-79.8% 缓+90.5%</v>
       </c>
     </row>
     <row r="36">
@@ -18098,13 +17958,13 @@
         <v>入 ¥12 · 出 ¥24 · 缓 ⚠</v>
       </c>
       <c r="G36" s="11" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="H36" s="11" t="str">
         <v>⚠ 入+300% 出+300%</v>
       </c>
       <c r="I36" s="11" t="str">
-        <v>✅ 一致(÷隐含)</v>
+        <v>⚠ 入+21.2% 出-19.2%</v>
       </c>
     </row>
     <row r="37">
@@ -24264,13 +24124,13 @@
         <v>入 $0.200 · 出 $0.400 · 缓 $0.04</v>
       </c>
       <c r="G30" s="15" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="H30" s="15" t="str">
         <v>⚠ 入+30% 出+30% 缓+1200%</v>
       </c>
       <c r="I30" s="15" t="str">
-        <v>⚠ 入+30% 出+30% 缓+1200%</v>
+        <v>⚠ 入-54.5% 出-69.7% 缓+185.7%</v>
       </c>
     </row>
     <row r="31">
@@ -24293,13 +24153,13 @@
         <v>入 $2.400 · 出 $4.800 · 缓 $0.2</v>
       </c>
       <c r="G31" s="15" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="H31" s="15" t="str">
         <v>⚠ 入+420% 出+420% 缓+5100%</v>
       </c>
       <c r="I31" s="15" t="str">
-        <v>⚠ 入+420% 出+420% 缓+5100.2%</v>
+        <v>⚠ 入+81.8% 出+21.2% 缓+354.5%</v>
       </c>
     </row>
     <row r="32">
@@ -26202,7 +26062,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I46"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -26293,13 +26153,13 @@
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.02</v>
       </c>
       <c r="G3" s="5" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="H3" s="5" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I3" s="5" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 出-33.3% 缓-37.1%</v>
       </c>
     </row>
     <row r="4">
@@ -26322,13 +26182,13 @@
         <v>入 ¥3 · 出 ¥6 · 缓 ¥0.025</v>
       </c>
       <c r="G4" s="5" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="H4" s="5" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I4" s="5" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 出-33.3% 缓-75%</v>
       </c>
     </row>
     <row r="5">
@@ -26974,28 +26834,28 @@
         <v>OpenAI</v>
       </c>
       <c r="B27" s="11" t="str">
-        <v>4.1（new）</v>
+        <v>5</v>
       </c>
       <c r="C27" s="11" t="str">
-        <v>gpt-4.1</v>
+        <v>gpt-5</v>
       </c>
       <c r="D27" s="11" t="str">
         <v>统一价</v>
       </c>
       <c r="E27" s="11" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F27" s="11" t="str">
-        <v>入 ¥15 · 出 ¥60 · 缓 ¥3.75</v>
+        <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
       </c>
       <c r="G27" s="11" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H27" s="11" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 缓-0.7%</v>
       </c>
       <c r="I27" s="11" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 缓-0.7%</v>
       </c>
     </row>
     <row r="28">
@@ -27003,28 +26863,28 @@
         <v>OpenAI</v>
       </c>
       <c r="B28" s="11" t="str">
-        <v>4o</v>
+        <v>5-nano</v>
       </c>
       <c r="C28" s="11" t="str">
-        <v>gpt-4o</v>
+        <v>gpt-5-nano</v>
       </c>
       <c r="D28" s="11" t="str">
         <v>统一价</v>
       </c>
       <c r="E28" s="11" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="F28" s="11" t="str">
-        <v>入 ¥18.75 · 出 ¥75 · 缓 ¥9.37</v>
+        <v>入 ¥0.37 · 出 ¥3 · 缓 ¥0.03</v>
       </c>
       <c r="G28" s="11" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="H28" s="11" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 入+13.8% 出+15.4% 缓-7.7%</v>
       </c>
       <c r="I28" s="11" t="str">
-        <v>✅ 一致(÷7.5)</v>
+        <v>⚠ 入+13.8% 出+15.4% 缓-7.7%</v>
       </c>
     </row>
     <row r="29">
@@ -27032,10 +26892,10 @@
         <v>OpenAI</v>
       </c>
       <c r="B29" s="11" t="str">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="C29" s="11" t="str">
-        <v>gpt-5</v>
+        <v>gpt-5.1</v>
       </c>
       <c r="D29" s="11" t="str">
         <v>统一价</v>
@@ -27044,16 +26904,16 @@
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F29" s="11" t="str">
-        <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
+        <v>入 ¥8.75 · 出 ¥70 · 缓 ¥0.87</v>
       </c>
       <c r="G29" s="11" t="str">
         <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H29" s="11" t="str">
-        <v>⚠ 缓-0.7%</v>
+        <v>⚠ 缓-0.6%</v>
       </c>
       <c r="I29" s="11" t="str">
-        <v>⚠ 缓-0.7%</v>
+        <v>⚠ 缓-0.6%</v>
       </c>
     </row>
     <row r="30">
@@ -27061,28 +26921,28 @@
         <v>OpenAI</v>
       </c>
       <c r="B30" s="11" t="str">
-        <v>5-nano</v>
+        <v>5.1-chat-latest（new）</v>
       </c>
       <c r="C30" s="11" t="str">
-        <v>gpt-5-nano</v>
+        <v>gpt-5.1-chat</v>
       </c>
       <c r="D30" s="11" t="str">
         <v>统一价</v>
       </c>
       <c r="E30" s="11" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F30" s="11" t="str">
-        <v>入 ¥0.37 · 出 ¥3 · 缓 ¥0.03</v>
+        <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
       </c>
       <c r="G30" s="11" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H30" s="11" t="str">
-        <v>⚠ 入+13.8% 出+15.4% 缓-7.7%</v>
+        <v>⚠ 缓-0.7%</v>
       </c>
       <c r="I30" s="11" t="str">
-        <v>⚠ 入+13.8% 出+15.4% 缓-7.7%</v>
+        <v>⚠ 缓-0.7%</v>
       </c>
     </row>
     <row r="31">
@@ -27090,28 +26950,28 @@
         <v>OpenAI</v>
       </c>
       <c r="B31" s="11" t="str">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="C31" s="11" t="str">
-        <v>gpt-5.1</v>
+        <v>gpt-5.2</v>
       </c>
       <c r="D31" s="11" t="str">
         <v>统一价</v>
       </c>
       <c r="E31" s="11" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="F31" s="11" t="str">
-        <v>入 ¥8.75 · 出 ¥70 · 缓 ¥0.87</v>
+        <v>入 ¥12.25 · 出 ¥98 · 缓 ¥1.22</v>
       </c>
       <c r="G31" s="11" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="H31" s="11" t="str">
-        <v>⚠ 缓-0.6%</v>
+        <v>✅ 一致(÷隐含)</v>
       </c>
       <c r="I31" s="11" t="str">
-        <v>⚠ 缓-0.6%</v>
+        <v>✅ 一致(÷隐含)</v>
       </c>
     </row>
     <row r="32">
@@ -27119,28 +26979,28 @@
         <v>OpenAI</v>
       </c>
       <c r="B32" s="11" t="str">
-        <v>5.1-chat-latest（new）</v>
+        <v>5.3-codex</v>
       </c>
       <c r="C32" s="11" t="str">
-        <v>gpt-5.1-chat</v>
+        <v>gpt-5.3-codex</v>
       </c>
       <c r="D32" s="11" t="str">
         <v>统一价</v>
       </c>
       <c r="E32" s="11" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="F32" s="11" t="str">
-        <v>入 ¥9.37 · 出 ¥75 · 缓 ¥0.93</v>
+        <v>入 ¥13.13 · 出 ¥105 · 缓 ¥1.35</v>
       </c>
       <c r="G32" s="11" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="H32" s="11" t="str">
-        <v>⚠ 缓-0.7%</v>
+        <v>⚠ 缓+2.8%</v>
       </c>
       <c r="I32" s="11" t="str">
-        <v>⚠ 缓-0.7%</v>
+        <v>⚠ 缓+2.8%</v>
       </c>
     </row>
     <row r="33">
@@ -27148,57 +27008,57 @@
         <v>OpenAI</v>
       </c>
       <c r="B33" s="11" t="str">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="C33" s="11" t="str">
-        <v>gpt-5.2</v>
+        <v>gpt-5.4</v>
       </c>
       <c r="D33" s="11" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E33" s="11" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="F33" s="11" t="str">
-        <v>入 ¥12.25 · 出 ¥98 · 缓 ¥1.22</v>
+        <v>入 ¥18.75 · 出 ¥112.5 · 缓 ¥1.88</v>
       </c>
       <c r="G33" s="11" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="H33" s="11" t="str">
-        <v>✅ 一致(÷隐含)</v>
+        <v>✅ 一致(÷7.5)</v>
       </c>
       <c r="I33" s="11" t="str">
-        <v>✅ 一致(÷隐含)</v>
+        <v>✅ 一致(÷7.5)</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="str">
-        <v>OpenAI</v>
+        <v/>
       </c>
       <c r="B34" s="11" t="str">
-        <v>5.3-codex</v>
+        <v/>
       </c>
       <c r="C34" s="11" t="str">
-        <v>gpt-5.3-codex</v>
+        <v/>
       </c>
       <c r="D34" s="11" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E34" s="11" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="F34" s="11" t="str">
-        <v>入 ¥13.13 · 出 ¥105 · 缓 ¥1.35</v>
+        <v>入 ¥37.5 · 出 ¥168.75 · 缓 ¥3.75</v>
       </c>
       <c r="G34" s="11" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="H34" s="11" t="str">
-        <v>⚠ 缓+2.8%</v>
+        <v>✅ 一致(÷7.5)</v>
       </c>
       <c r="I34" s="11" t="str">
-        <v>⚠ 缓+2.8%</v>
+        <v>✅ 一致(÷7.5)</v>
       </c>
     </row>
     <row r="35">
@@ -27206,22 +27066,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B35" s="11" t="str">
-        <v>5.4</v>
+        <v>5.4-mini</v>
       </c>
       <c r="C35" s="11" t="str">
-        <v>gpt-5.4</v>
+        <v>gpt-5.4-mini</v>
       </c>
       <c r="D35" s="11" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E35" s="11" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="F35" s="11" t="str">
-        <v>入 ¥18.75 · 出 ¥112.5 · 缓 ¥1.88</v>
+        <v>入 ¥5.63 · 出 ¥33.75 · 缓 ¥0.56</v>
       </c>
       <c r="G35" s="11" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="H35" s="11" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -27232,25 +27092,25 @@
     </row>
     <row r="36">
       <c r="A36" s="11" t="str">
-        <v/>
+        <v>OpenAI</v>
       </c>
       <c r="B36" s="11" t="str">
-        <v/>
+        <v>5.4-nano</v>
       </c>
       <c r="C36" s="11" t="str">
-        <v/>
+        <v>gpt-5.4-nano</v>
       </c>
       <c r="D36" s="11" t="str">
-        <v>输入&gt;272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E36" s="11" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
       <c r="F36" s="11" t="str">
-        <v>入 ¥37.5 · 出 ¥168.75 · 缓 ¥3.75</v>
+        <v>入 ¥1.5 · 出 ¥9.375 · 缓 ¥0.15</v>
       </c>
       <c r="G36" s="11" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
       <c r="H36" s="11" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -27264,22 +27124,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B37" s="11" t="str">
-        <v>5.4-mini</v>
+        <v>5.4-pro</v>
       </c>
       <c r="C37" s="11" t="str">
-        <v>gpt-5.4-mini</v>
+        <v>gpt-5.4-pro</v>
       </c>
       <c r="D37" s="11" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E37" s="11" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="F37" s="11" t="str">
-        <v>入 ¥5.63 · 出 ¥33.75 · 缓 ¥0.56</v>
+        <v>入 ¥225 · 出 ¥1350 · 缓 ⚠</v>
       </c>
       <c r="G37" s="11" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $30 · 出 $180 · 缓 ⚠</v>
       </c>
       <c r="H37" s="11" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -27290,25 +27150,25 @@
     </row>
     <row r="38">
       <c r="A38" s="11" t="str">
-        <v>OpenAI</v>
+        <v/>
       </c>
       <c r="B38" s="11" t="str">
-        <v>5.4-nano</v>
+        <v/>
       </c>
       <c r="C38" s="11" t="str">
-        <v>gpt-5.4-nano</v>
+        <v/>
       </c>
       <c r="D38" s="11" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E38" s="11" t="str">
-        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="F38" s="11" t="str">
-        <v>入 ¥1.5 · 出 ¥9.375 · 缓 ¥0.15</v>
+        <v>入 ¥450 · 出 ¥2025 · 缓 ⚠</v>
       </c>
       <c r="G38" s="11" t="str">
-        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
+        <v>入 $60 · 出 $270 · 缓 ⚠</v>
       </c>
       <c r="H38" s="11" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -27322,22 +27182,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B39" s="11" t="str">
-        <v>5.4-pro</v>
+        <v>5.5（new）</v>
       </c>
       <c r="C39" s="11" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>gpt-5.5</v>
       </c>
       <c r="D39" s="11" t="str">
         <v>输入&lt;=272K context</v>
       </c>
       <c r="E39" s="11" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="F39" s="11" t="str">
-        <v>入 ¥225 · 出 ¥1350 · 缓 ⚠</v>
+        <v>入 ¥37.5 · 出 ¥225 · 缓 ¥3.75</v>
       </c>
       <c r="G39" s="11" t="str">
-        <v>入 $30 · 出 $180 · 缓 ⚠</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="H39" s="11" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -27360,13 +27220,13 @@
         <v>输入&gt;272K context</v>
       </c>
       <c r="E40" s="11" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="F40" s="11" t="str">
-        <v>入 ¥450 · 出 ¥2025 · 缓 ⚠</v>
+        <v>入 ¥75 · 出 ¥337.5 · 缓 ¥7.5</v>
       </c>
       <c r="G40" s="11" t="str">
-        <v>入 $60 · 出 $270 · 缓 ⚠</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="H40" s="11" t="str">
         <v>✅ 一致(÷7.5)</v>
@@ -27376,84 +27236,84 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="str">
-        <v>OpenAI</v>
-      </c>
-      <c r="B41" s="11" t="str">
-        <v>5.5（new）</v>
-      </c>
-      <c r="C41" s="11" t="str">
-        <v>gpt-5.5</v>
-      </c>
-      <c r="D41" s="11" t="str">
-        <v>输入&lt;=272K context</v>
-      </c>
-      <c r="E41" s="11" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
-      </c>
-      <c r="F41" s="11" t="str">
-        <v>入 ¥37.5 · 出 ¥225 · 缓 ¥3.75</v>
-      </c>
-      <c r="G41" s="11" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
-      </c>
-      <c r="H41" s="11" t="str">
-        <v>✅ 一致(÷7.5)</v>
-      </c>
-      <c r="I41" s="11" t="str">
-        <v>✅ 一致(÷7.5)</v>
+      <c r="A41" s="13" t="str">
+        <v>Tencent</v>
+      </c>
+      <c r="B41" s="13" t="str">
+        <v>3-preview</v>
+      </c>
+      <c r="C41" s="13" t="str">
+        <v>hy3-preview</v>
+      </c>
+      <c r="D41" s="13" t="str">
+        <v>输入&lt;16k</v>
+      </c>
+      <c r="E41" s="13" t="str">
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+      </c>
+      <c r="F41" s="13" t="str">
+        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+      </c>
+      <c r="G41" s="13" t="str">
+        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
+      </c>
+      <c r="H41" s="13" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="I41" s="13" t="str">
+        <v>✅ 一致</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="str">
-        <v/>
-      </c>
-      <c r="B42" s="11" t="str">
-        <v/>
-      </c>
-      <c r="C42" s="11" t="str">
-        <v/>
-      </c>
-      <c r="D42" s="11" t="str">
-        <v>输入&gt;272K context</v>
-      </c>
-      <c r="E42" s="11" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
-      </c>
-      <c r="F42" s="11" t="str">
-        <v>入 ¥75 · 出 ¥337.5 · 缓 ¥7.5</v>
-      </c>
-      <c r="G42" s="11" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
-      </c>
-      <c r="H42" s="11" t="str">
-        <v>✅ 一致(÷7.5)</v>
-      </c>
-      <c r="I42" s="11" t="str">
-        <v>✅ 一致(÷7.5)</v>
+      <c r="A42" s="13" t="str">
+        <v/>
+      </c>
+      <c r="B42" s="13" t="str">
+        <v/>
+      </c>
+      <c r="C42" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D42" s="13" t="str">
+        <v>16k&lt;=输入&lt;32k</v>
+      </c>
+      <c r="E42" s="13" t="str">
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+      </c>
+      <c r="F42" s="13" t="str">
+        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
+      </c>
+      <c r="G42" s="13" t="str">
+        <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
+      </c>
+      <c r="H42" s="13" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="I42" s="13" t="str">
+        <v>✅ 一致</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="str">
-        <v>Tencent</v>
+        <v/>
       </c>
       <c r="B43" s="13" t="str">
-        <v>3-preview</v>
+        <v/>
       </c>
       <c r="C43" s="13" t="str">
-        <v>hy3-preview</v>
+        <v/>
       </c>
       <c r="D43" s="13" t="str">
-        <v>输入&lt;16k</v>
+        <v>输入&gt;=32k</v>
       </c>
       <c r="E43" s="13" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="F43" s="13" t="str">
-        <v>入 ¥1.2 · 出 ¥4 · 缓 ¥0.4</v>
+        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
       </c>
       <c r="G43" s="13" t="str">
-        <v>入 $0.184615 · 出 $0.615385 · 缓 $0.061538</v>
+        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
       </c>
       <c r="H43" s="13" t="str">
         <v>✅ 一致</v>
@@ -27463,147 +27323,89 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B44" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C44" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D44" s="13" t="str">
-        <v>16k&lt;=输入&lt;32k</v>
-      </c>
-      <c r="E44" s="13" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
-      </c>
-      <c r="F44" s="13" t="str">
-        <v>入 ¥1.6 · 出 ¥6.4 · 缓 ¥0.6</v>
-      </c>
-      <c r="G44" s="13" t="str">
-        <v>入 $0.246154 · 出 $0.984615 · 缓 $0.092308</v>
-      </c>
-      <c r="H44" s="13" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="I44" s="13" t="str">
+      <c r="A44" s="15" t="str">
+        <v>Moonshot AI</v>
+      </c>
+      <c r="B44" s="15" t="str">
+        <v>k1.5 (普通搜索)</v>
+      </c>
+      <c r="C44" s="15" t="str">
+        <v>kimi-k2.5</v>
+      </c>
+      <c r="D44" s="15" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E44" s="15" t="str">
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+      </c>
+      <c r="F44" s="15" t="str">
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+      </c>
+      <c r="G44" s="15" t="str">
+        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
+      </c>
+      <c r="H44" s="15" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="I44" s="15" t="str">
         <v>✅ 一致</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B45" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C45" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D45" s="13" t="str">
-        <v>输入&gt;=32k</v>
-      </c>
-      <c r="E45" s="13" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
-      </c>
-      <c r="F45" s="13" t="str">
-        <v>入 ¥2 · 出 ¥8 · 缓 ¥0.8</v>
-      </c>
-      <c r="G45" s="13" t="str">
-        <v>入 $0.307692 · 出 $1.230769 · 缓 $0.123077</v>
-      </c>
-      <c r="H45" s="13" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="I45" s="13" t="str">
+      <c r="A45" s="17" t="str">
+        <v>MiniMax</v>
+      </c>
+      <c r="B45" s="17" t="str">
+        <v>M2.5</v>
+      </c>
+      <c r="C45" s="17" t="str">
+        <v>minimax-m2.5</v>
+      </c>
+      <c r="D45" s="17" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E45" s="17" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+      </c>
+      <c r="F45" s="17" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+      </c>
+      <c r="G45" s="17" t="str">
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
+      </c>
+      <c r="H45" s="17" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="I45" s="17" t="str">
         <v>✅ 一致</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="str">
-        <v>Moonshot AI</v>
-      </c>
-      <c r="B46" s="15" t="str">
-        <v>k1.5 (普通搜索)</v>
-      </c>
-      <c r="C46" s="15" t="str">
-        <v>kimi-k2.5</v>
-      </c>
-      <c r="D46" s="15" t="str">
+      <c r="A46" s="17" t="str">
+        <v>MiniMax</v>
+      </c>
+      <c r="B46" s="17" t="str">
+        <v>M2.7</v>
+      </c>
+      <c r="C46" s="17" t="str">
+        <v>minimax-m2.7</v>
+      </c>
+      <c r="D46" s="17" t="str">
         <v>统一价</v>
       </c>
-      <c r="E46" s="15" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
-      </c>
-      <c r="F46" s="15" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
-      </c>
-      <c r="G46" s="15" t="str">
-        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
-      </c>
-      <c r="H46" s="15" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="I46" s="15" t="str">
-        <v>✅ 一致</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="17" t="str">
-        <v>MiniMax</v>
-      </c>
-      <c r="B47" s="17" t="str">
-        <v>M2.5</v>
-      </c>
-      <c r="C47" s="17" t="str">
-        <v>minimax-m2.5</v>
-      </c>
-      <c r="D47" s="17" t="str">
-        <v>统一价</v>
-      </c>
-      <c r="E47" s="17" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
-      </c>
-      <c r="F47" s="17" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
-      </c>
-      <c r="G47" s="17" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
-      </c>
-      <c r="H47" s="17" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="I47" s="17" t="str">
-        <v>✅ 一致</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="str">
-        <v>MiniMax</v>
-      </c>
-      <c r="B48" s="17" t="str">
-        <v>M2.7</v>
-      </c>
-      <c r="C48" s="17" t="str">
-        <v>minimax-m2.7</v>
-      </c>
-      <c r="D48" s="17" t="str">
-        <v>统一价</v>
-      </c>
-      <c r="E48" s="17" t="str">
+      <c r="E46" s="17" t="str">
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
-      <c r="F48" s="17" t="str">
+      <c r="F46" s="17" t="str">
         <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
       </c>
-      <c r="G48" s="17" t="str">
+      <c r="G46" s="17" t="str">
         <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
       </c>
-      <c r="H48" s="17" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="I48" s="17" t="str">
+      <c r="H46" s="17" t="str">
+        <v>✅ 一致</v>
+      </c>
+      <c r="I46" s="17" t="str">
         <v>✅ 一致</v>
       </c>
     </row>
@@ -27639,28 +27441,28 @@
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="C25:C26"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I47"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -27670,7 +27472,7 @@
     <col min="6" max="6" width="35.83203125" customWidth="1"/>
     <col min="7" max="7" width="44.83203125" customWidth="1"/>
     <col min="8" max="8" width="28.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27867,13 +27669,13 @@
         <v>入 $0.154 · 出 $0.308 · 缓 $0.003</v>
       </c>
       <c r="G7" s="7" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="H7" s="7" t="str">
         <v>⚠ 缓-2.5%</v>
       </c>
       <c r="I7" s="7" t="str">
-        <v>⚠ 缓-2.5%</v>
+        <v>⚠ 入-65% 出-76.7% 缓-78.6%</v>
       </c>
     </row>
     <row r="8">
@@ -27896,13 +27698,13 @@
         <v>入 $0.462 · 出 $0.923 · 缓 $0.004</v>
       </c>
       <c r="G8" s="7" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="H8" s="7" t="str">
         <v>⚠ 缓+4%</v>
       </c>
       <c r="I8" s="7" t="str">
-        <v>⚠ 缓+4%</v>
+        <v>⚠ 入-65% 出-76.7% 缓-90.9%</v>
       </c>
     </row>
     <row r="9">
@@ -28548,22 +28350,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B31" s="13" t="str">
-        <v>4.1（new）</v>
+        <v>5</v>
       </c>
       <c r="C31" s="13" t="str">
-        <v>gpt-4.1</v>
+        <v>gpt-5</v>
       </c>
       <c r="D31" s="13" t="str">
         <v>统一价</v>
       </c>
       <c r="E31" s="13" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F31" s="13" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G31" s="13" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H31" s="13" t="str">
         <v>✅ 一致</v>
@@ -28577,22 +28379,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B32" s="13" t="str">
-        <v>4o</v>
+        <v>5-nano</v>
       </c>
       <c r="C32" s="13" t="str">
-        <v>gpt-4o</v>
+        <v>gpt-5-nano</v>
       </c>
       <c r="D32" s="13" t="str">
         <v>统一价</v>
       </c>
       <c r="E32" s="13" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="F32" s="13" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="G32" s="13" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
       </c>
       <c r="H32" s="13" t="str">
         <v>✅ 一致</v>
@@ -28606,10 +28408,10 @@
         <v>OpenAI</v>
       </c>
       <c r="B33" s="13" t="str">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="C33" s="13" t="str">
-        <v>gpt-5</v>
+        <v>gpt-5.1</v>
       </c>
       <c r="D33" s="13" t="str">
         <v>统一价</v>
@@ -28635,22 +28437,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B34" s="13" t="str">
-        <v>5-nano</v>
+        <v>5.1-chat-latest（new）</v>
       </c>
       <c r="C34" s="13" t="str">
-        <v>gpt-5-nano</v>
+        <v>gpt-5.1-chat</v>
       </c>
       <c r="D34" s="13" t="str">
         <v>统一价</v>
       </c>
       <c r="E34" s="13" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="F34" s="13" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="G34" s="13" t="str">
-        <v>入 $0.05 · 出 $0.4 · 缓 $0.005</v>
+        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
       </c>
       <c r="H34" s="13" t="str">
         <v>✅ 一致</v>
@@ -28664,22 +28466,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B35" s="13" t="str">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="C35" s="13" t="str">
-        <v>gpt-5.1</v>
+        <v>gpt-5.2</v>
       </c>
       <c r="D35" s="13" t="str">
         <v>统一价</v>
       </c>
       <c r="E35" s="13" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="F35" s="13" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="G35" s="13" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="H35" s="13" t="str">
         <v>✅ 一致</v>
@@ -28693,28 +28495,28 @@
         <v>OpenAI</v>
       </c>
       <c r="B36" s="13" t="str">
-        <v>5.1-chat-latest（new）</v>
+        <v>5.3-codex</v>
       </c>
       <c r="C36" s="13" t="str">
-        <v>gpt-5.1-chat</v>
+        <v>gpt-5.3-codex</v>
       </c>
       <c r="D36" s="13" t="str">
         <v>统一价</v>
       </c>
       <c r="E36" s="13" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="F36" s="13" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
       </c>
       <c r="G36" s="13" t="str">
-        <v>入 $1.25 · 出 $10 · 缓 $0.125</v>
+        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
       </c>
       <c r="H36" s="13" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓+2.9%</v>
       </c>
       <c r="I36" s="13" t="str">
-        <v>✅ 一致</v>
+        <v>⚠ 缓+2.9%</v>
       </c>
     </row>
     <row r="37">
@@ -28722,22 +28524,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B37" s="13" t="str">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="C37" s="13" t="str">
-        <v>gpt-5.2</v>
+        <v>gpt-5.4</v>
       </c>
       <c r="D37" s="13" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E37" s="13" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="F37" s="13" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="G37" s="13" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
       </c>
       <c r="H37" s="13" t="str">
         <v>✅ 一致</v>
@@ -28748,31 +28550,31 @@
     </row>
     <row r="38">
       <c r="A38" s="13" t="str">
-        <v>OpenAI</v>
+        <v/>
       </c>
       <c r="B38" s="13" t="str">
-        <v>5.3-codex</v>
+        <v/>
       </c>
       <c r="C38" s="13" t="str">
-        <v>gpt-5.3-codex</v>
+        <v/>
       </c>
       <c r="D38" s="13" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E38" s="13" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="F38" s="13" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.18</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="G38" s="13" t="str">
-        <v>入 $1.75 · 出 $14 · 缓 $0.175</v>
+        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
       </c>
       <c r="H38" s="13" t="str">
-        <v>⚠ 缓+2.9%</v>
+        <v>✅ 一致</v>
       </c>
       <c r="I38" s="13" t="str">
-        <v>⚠ 缓+2.9%</v>
+        <v>✅ 一致</v>
       </c>
     </row>
     <row r="39">
@@ -28780,22 +28582,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B39" s="13" t="str">
-        <v>5.4</v>
+        <v>5.4-mini</v>
       </c>
       <c r="C39" s="13" t="str">
-        <v>gpt-5.4</v>
+        <v>gpt-5.4-mini</v>
       </c>
       <c r="D39" s="13" t="str">
-        <v>输入&lt;=272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E39" s="13" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="F39" s="13" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="G39" s="13" t="str">
-        <v>入 $2.5 · 出 $15 · 缓 $0.25</v>
+        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
       </c>
       <c r="H39" s="13" t="str">
         <v>✅ 一致</v>
@@ -28806,25 +28608,25 @@
     </row>
     <row r="40">
       <c r="A40" s="13" t="str">
-        <v/>
+        <v>OpenAI</v>
       </c>
       <c r="B40" s="13" t="str">
-        <v/>
+        <v>5.4-nano</v>
       </c>
       <c r="C40" s="13" t="str">
-        <v/>
+        <v>gpt-5.4-nano</v>
       </c>
       <c r="D40" s="13" t="str">
-        <v>输入&gt;272K context</v>
+        <v>统一价</v>
       </c>
       <c r="E40" s="13" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
       <c r="F40" s="13" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
       <c r="G40" s="13" t="str">
-        <v>入 $5 · 出 $22.5 · 缓 $0.5</v>
+        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
       </c>
       <c r="H40" s="13" t="str">
         <v>✅ 一致</v>
@@ -28838,22 +28640,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B41" s="13" t="str">
-        <v>5.4-mini</v>
+        <v>5.4-pro</v>
       </c>
       <c r="C41" s="13" t="str">
-        <v>gpt-5.4-mini</v>
+        <v>gpt-5.4-pro</v>
       </c>
       <c r="D41" s="13" t="str">
-        <v>统一价</v>
+        <v>输入&lt;=272K context</v>
       </c>
       <c r="E41" s="13" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $30 · 出 $180</v>
       </c>
       <c r="F41" s="13" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $30 · 出 $180 · 缓 ⚠</v>
       </c>
       <c r="G41" s="13" t="str">
-        <v>入 $0.75 · 出 $4.5 · 缓 $0.075</v>
+        <v>入 $30 · 出 $180 · 缓 ⚠</v>
       </c>
       <c r="H41" s="13" t="str">
         <v>✅ 一致</v>
@@ -28864,25 +28666,25 @@
     </row>
     <row r="42">
       <c r="A42" s="13" t="str">
-        <v>OpenAI</v>
+        <v/>
       </c>
       <c r="B42" s="13" t="str">
-        <v>5.4-nano</v>
+        <v/>
       </c>
       <c r="C42" s="13" t="str">
-        <v>gpt-5.4-nano</v>
+        <v/>
       </c>
       <c r="D42" s="13" t="str">
-        <v>统一价</v>
+        <v>输入&gt;272K context</v>
       </c>
       <c r="E42" s="13" t="str">
-        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
+        <v>入 $60 · 出 $270</v>
       </c>
       <c r="F42" s="13" t="str">
-        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
+        <v>入 $60 · 出 $270 · 缓 ⚠</v>
       </c>
       <c r="G42" s="13" t="str">
-        <v>入 $0.2 · 出 $1.25 · 缓 $0.02</v>
+        <v>入 $60 · 出 $270 · 缓 ⚠</v>
       </c>
       <c r="H42" s="13" t="str">
         <v>✅ 一致</v>
@@ -28896,22 +28698,22 @@
         <v>OpenAI</v>
       </c>
       <c r="B43" s="13" t="str">
-        <v>5.4-pro</v>
+        <v>5.5（new）</v>
       </c>
       <c r="C43" s="13" t="str">
-        <v>gpt-5.4-pro</v>
+        <v>gpt-5.5</v>
       </c>
       <c r="D43" s="13" t="str">
         <v>输入&lt;=272K context</v>
       </c>
       <c r="E43" s="13" t="str">
-        <v>入 $30 · 出 $180</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="F43" s="13" t="str">
-        <v>入 $30 · 出 $180 · 缓 ⚠</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="G43" s="13" t="str">
-        <v>入 $30 · 出 $180 · 缓 ⚠</v>
+        <v>入 $5 · 出 $30 · 缓 $0.5</v>
       </c>
       <c r="H43" s="13" t="str">
         <v>✅ 一致</v>
@@ -28934,13 +28736,13 @@
         <v>输入&gt;272K context</v>
       </c>
       <c r="E44" s="13" t="str">
-        <v>入 $60 · 出 $270</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="F44" s="13" t="str">
-        <v>入 $60 · 出 $270 · 缓 ⚠</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="G44" s="13" t="str">
-        <v>入 $60 · 出 $270 · 缓 ⚠</v>
+        <v>入 $10 · 出 $45 · 缓 $1</v>
       </c>
       <c r="H44" s="13" t="str">
         <v>✅ 一致</v>
@@ -28950,147 +28752,89 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="str">
-        <v>OpenAI</v>
-      </c>
-      <c r="B45" s="13" t="str">
-        <v>5.5（new）</v>
-      </c>
-      <c r="C45" s="13" t="str">
-        <v>gpt-5.5</v>
-      </c>
-      <c r="D45" s="13" t="str">
-        <v>输入&lt;=272K context</v>
-      </c>
-      <c r="E45" s="13" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
-      </c>
-      <c r="F45" s="13" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
-      </c>
-      <c r="G45" s="13" t="str">
-        <v>入 $5 · 出 $30 · 缓 $0.5</v>
-      </c>
-      <c r="H45" s="13" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="I45" s="13" t="str">
+      <c r="A45" s="15" t="str">
+        <v>Moonshot AI</v>
+      </c>
+      <c r="B45" s="15" t="str">
+        <v>k1.5 (普通搜索)</v>
+      </c>
+      <c r="C45" s="15" t="str">
+        <v>kimi-k2.5</v>
+      </c>
+      <c r="D45" s="15" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E45" s="15" t="str">
+        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
+      </c>
+      <c r="F45" s="15" t="str">
+        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
+      </c>
+      <c r="G45" s="15" t="str">
+        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
+      </c>
+      <c r="H45" s="15" t="str">
+        <v>✅ 一致(÷6.5)</v>
+      </c>
+      <c r="I45" s="15" t="str">
         <v>✅ 一致</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B46" s="13" t="str">
-        <v/>
-      </c>
-      <c r="C46" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D46" s="13" t="str">
-        <v>输入&gt;272K context</v>
-      </c>
-      <c r="E46" s="13" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
-      </c>
-      <c r="F46" s="13" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
-      </c>
-      <c r="G46" s="13" t="str">
-        <v>入 $10 · 出 $45 · 缓 $1</v>
-      </c>
-      <c r="H46" s="13" t="str">
-        <v>✅ 一致</v>
-      </c>
-      <c r="I46" s="13" t="str">
-        <v>✅ 一致</v>
+      <c r="A46" s="17" t="str">
+        <v>MiniMax</v>
+      </c>
+      <c r="B46" s="17" t="str">
+        <v>M2.5</v>
+      </c>
+      <c r="C46" s="17" t="str">
+        <v>minimax-m2.5</v>
+      </c>
+      <c r="D46" s="17" t="str">
+        <v>统一价</v>
+      </c>
+      <c r="E46" s="17" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
+      </c>
+      <c r="F46" s="17" t="str">
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
+      </c>
+      <c r="G46" s="17" t="str">
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
+      </c>
+      <c r="H46" s="17" t="str">
+        <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
+      </c>
+      <c r="I46" s="17" t="str">
+        <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="str">
-        <v>Moonshot AI</v>
-      </c>
-      <c r="B47" s="15" t="str">
-        <v>k1.5 (普通搜索)</v>
-      </c>
-      <c r="C47" s="15" t="str">
-        <v>kimi-k2.5</v>
-      </c>
-      <c r="D47" s="15" t="str">
+      <c r="A47" s="17" t="str">
+        <v>MiniMax</v>
+      </c>
+      <c r="B47" s="17" t="str">
+        <v>M2.7</v>
+      </c>
+      <c r="C47" s="17" t="str">
+        <v>minimax-m2.7</v>
+      </c>
+      <c r="D47" s="17" t="str">
         <v>统一价</v>
       </c>
-      <c r="E47" s="15" t="str">
-        <v>入 ¥4 · 出 ¥21 · 缓 ¥0.7</v>
-      </c>
-      <c r="F47" s="15" t="str">
-        <v>入 $0.616 · 出 $3.234 · 缓 $0.108</v>
-      </c>
-      <c r="G47" s="15" t="str">
-        <v>入 $0.615385 · 出 $3.230769 · 缓 $0.107692</v>
-      </c>
-      <c r="H47" s="15" t="str">
-        <v>✅ 一致(÷6.5)</v>
-      </c>
-      <c r="I47" s="15" t="str">
-        <v>✅ 一致</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="str">
-        <v>MiniMax</v>
-      </c>
-      <c r="B48" s="17" t="str">
-        <v>M2.5</v>
-      </c>
-      <c r="C48" s="17" t="str">
-        <v>minimax-m2.5</v>
-      </c>
-      <c r="D48" s="17" t="str">
-        <v>统一价</v>
-      </c>
-      <c r="E48" s="17" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.21</v>
-      </c>
-      <c r="F48" s="17" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.03</v>
-      </c>
-      <c r="G48" s="17" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.032308</v>
-      </c>
-      <c r="H48" s="17" t="str">
+      <c r="E47" s="17" t="str">
+        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
+      </c>
+      <c r="F47" s="17" t="str">
+        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
+      </c>
+      <c r="G47" s="17" t="str">
+        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
+      </c>
+      <c r="H47" s="17" t="str">
         <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
       </c>
-      <c r="I48" s="17" t="str">
-        <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="17" t="str">
-        <v>MiniMax</v>
-      </c>
-      <c r="B49" s="17" t="str">
-        <v>M2.7</v>
-      </c>
-      <c r="C49" s="17" t="str">
-        <v>minimax-m2.7</v>
-      </c>
-      <c r="D49" s="17" t="str">
-        <v>统一价</v>
-      </c>
-      <c r="E49" s="17" t="str">
-        <v>入 ¥2.1 · 出 ¥8.4 · 缓 ¥0.42</v>
-      </c>
-      <c r="F49" s="17" t="str">
-        <v>入 $0.3 · 出 $1.2 · 缓 $0.06</v>
-      </c>
-      <c r="G49" s="17" t="str">
-        <v>入 $0.323077 · 出 $1.292308 · 缓 $0.064615</v>
-      </c>
-      <c r="H49" s="17" t="str">
-        <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
-      </c>
-      <c r="I49" s="17" t="str">
+      <c r="I47" s="17" t="str">
         <v>⚠ 入-7.1% 出-7.1% 缓-7.1%</v>
       </c>
     </row>
@@ -29126,18 +28870,18 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C43:C44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -29154,7 +28898,7 @@
     <col min="6" max="6" width="31.83203125" customWidth="1"/>
     <col min="7" max="7" width="44.83203125" customWidth="1"/>
     <col min="8" max="8" width="29.83203125" customWidth="1"/>
-    <col min="9" max="9" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29351,13 +29095,13 @@
         <v>入 ¥1 · 出 ¥2 · 缓 ¥0.2</v>
       </c>
       <c r="G7" s="5" t="str">
-        <v>入 $0.153846 · 出 $0.307692 · 缓 $0.003077</v>
+        <v>入 $0.44 · 出 $1.32 · 缓 $0.014</v>
       </c>
       <c r="H7" s="5" t="str">
         <v>⚠ 缓+900%</v>
       </c>
       <c r="I7" s="5" t="str">
-        <v>⚠ 入-13.3% 出-13.3% 缓+766.6%</v>
+        <v>⚠ 入-69.7% 出-79.8% 缓+90.5%</v>
       </c>
     </row>
     <row r="8">
@@ -29380,13 +29124,13 @@
         <v>入 ¥12 · 出 ¥24 · 缓 ¥1</v>
       </c>
       <c r="G8" s="5" t="str">
-        <v>入 $0.461538 · 出 $0.923077 · 缓 $0.003846</v>
+        <v>入 $1.32 · 出 $3.96 · 缓 $0.044</v>
       </c>
       <c r="H8" s="5" t="str">
         <v>⚠ 入+300% 出+300% 缓+3900%</v>
       </c>
       <c r="I8" s="5" t="str">
-        <v>⚠ 缓+900%</v>
+        <v>⚠ 出-33.3% 缓+150%</v>
       </c>
     </row>
     <row r="9">
@@ -31386,13 +31130,13 @@
         <v>入 $2 · 出 $8 · 缓 $0.5</v>
       </c>
       <c r="G21" s="5" t="str">
-        <v>入 $2 · 出 $8 · 缓 $0.5</v>
+        <v>—</v>
       </c>
       <c r="H21" s="5" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I21" s="5" t="str">
-        <v>✅ 一致</v>
+        <v>—</v>
       </c>
     </row>
     <row r="22">
@@ -31415,13 +31159,13 @@
         <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
       </c>
       <c r="G22" s="5" t="str">
-        <v>入 $2.5 · 出 $10 · 缓 $1.25</v>
+        <v>—</v>
       </c>
       <c r="H22" s="5" t="str">
         <v>✅ 一致</v>
       </c>
       <c r="I22" s="5" t="str">
-        <v>✅ 一致</v>
+        <v>—</v>
       </c>
     </row>
     <row r="23">
